--- a/backtest/results_172/七星172_交易记录_2026.xlsx
+++ b/backtest/results_172/七星172_交易记录_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G64"/>
+  <dimension ref="A1:G66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2496,6 +2496,72 @@
         </is>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>科创50ETF易方达</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>sh588080</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>1.822</v>
+      </c>
+      <c r="F65" t="n">
+        <v>11.2327</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>盈利保护(回撤超5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>创业板成长ETF华夏</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>sz159967</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F66" t="n">
+        <v>5.0321</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>动量排名第1/38</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backtest/results_172/七星172_交易记录_2026.xlsx
+++ b/backtest/results_172/七星172_交易记录_2026.xlsx
@@ -456,7 +456,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-06 09:30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -489,7 +489,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-09 09:30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -522,7 +522,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-09 09:30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -555,7 +555,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-10 09:30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -586,7 +586,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-10 09:30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -619,7 +619,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-11 09:30</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -650,7 +650,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-11 09:30</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -683,7 +683,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-13 09:30</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -716,7 +716,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-13 09:30</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -749,7 +749,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-26 09:30</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -780,7 +780,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-26 09:30</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -813,7 +813,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-27 09:30</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -846,7 +846,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-27 09:30</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -879,7 +879,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-02 09:30</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -910,7 +910,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-02 09:30</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -943,7 +943,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-04 09:30</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -974,7 +974,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-04 09:30</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1007,7 +1007,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-05 09:30</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1040,7 +1040,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-05 09:30</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1073,7 +1073,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-09 09:30</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1104,7 +1104,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-10 09:30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1137,7 +1137,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-11 09:30</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1170,7 +1170,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-11 09:30</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1203,7 +1203,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-12 09:30</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1236,7 +1236,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-12 09:30</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1269,7 +1269,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-16 09:30</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1300,7 +1300,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-16 09:30</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1333,7 +1333,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-24 09:30</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1364,7 +1364,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-24 09:30</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1397,7 +1397,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-25 09:30</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1430,7 +1430,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-25 09:30</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1463,7 +1463,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-27 09:30</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1494,7 +1494,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-30 09:30</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1527,7 +1527,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-31 09:30</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1558,7 +1558,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-31 09:30</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1591,7 +1591,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-03 09:30</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1624,7 +1624,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-03 09:30</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1657,7 +1657,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-07 09:30</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1688,7 +1688,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-07 09:30</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1721,7 +1721,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-08 09:30</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1752,7 +1752,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-08 09:30</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-24 09:30</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1816,7 +1816,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-24 09:30</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1849,7 +1849,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-27 09:30</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1882,7 +1882,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-27 09:30</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-30 09:30</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1946,7 +1946,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-30 09:30</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1979,7 +1979,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-06 09:30</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2010,7 +2010,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-06 09:30</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2043,7 +2043,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-12 09:30</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2074,7 +2074,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-12 09:30</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2107,7 +2107,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-15 09:30</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2138,7 +2138,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-15 09:30</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2171,7 +2171,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-18 09:30</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2204,7 +2204,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-18 09:30</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2237,7 +2237,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-21 09:30</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2268,7 +2268,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-21 09:30</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2301,7 +2301,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-25 09:30</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2334,7 +2334,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-25 09:30</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2367,7 +2367,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-27 09:30</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2400,7 +2400,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-27 09:30</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2433,7 +2433,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-28 09:30</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2466,7 +2466,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-28 09:30</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2499,7 +2499,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-29 09:33</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2532,7 +2532,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-29 09:33</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">

--- a/backtest/results_172/七星172_交易记录_2026.xlsx
+++ b/backtest/results_172/七星172_交易记录_2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G66"/>
+  <dimension ref="A1:G214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,17 +456,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-02-06 09:30</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>港股红利ETF博时</t>
+          <t>恒生科技ETF华泰柏瑞</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>sh513690</t>
+          <t>sh513130</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -475,31 +475,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1.153</v>
+        <v>0.713</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0237</v>
+        <v>10.1885</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>动量排名第1/6</t>
+          <t>动量排名第1/39</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-02-09 09:30</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>港股红利ETF博时</t>
+          <t>恒生科技ETF华泰柏瑞</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>sh513690</t>
+          <t>sh513130</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -508,10 +508,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1.166</v>
+        <v>0.73</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1296</v>
+        <v>11.4403</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -522,17 +522,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-02-09 09:30</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>中韩半导体ETF华泰柏瑞</t>
+          <t>港股通互联网ETF富国</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>sh513310</t>
+          <t>sz159792</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -541,31 +541,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3.533</v>
+        <v>0.876</v>
       </c>
       <c r="F4" t="n">
-        <v>4.8407</v>
+        <v>12.663</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>动量排名第1/11</t>
+          <t>动量排名第1/39</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-02-10 09:30</t>
+          <t>2025-02-17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>中韩半导体ETF华泰柏瑞</t>
+          <t>港股通互联网ETF富国</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>sh513310</t>
+          <t>sz159792</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3.489</v>
+        <v>0.885</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
@@ -586,17 +586,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-02-10 09:30</t>
+          <t>2025-02-17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>南方原油LOF</t>
+          <t>恒生科技ETF华泰柏瑞</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>sh501018</t>
+          <t>sh513130</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -605,31 +605,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.395</v>
+        <v>0.738</v>
       </c>
       <c r="F6" t="n">
-        <v>4.7504</v>
+        <v>14.4242</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>动量排名第1/6</t>
+          <t>动量排名第1/39</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-02-11 09:30</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>南方原油LOF</t>
+          <t>恒生科技ETF华泰柏瑞</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>sh501018</t>
+          <t>sh513130</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -638,9 +638,11 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1.348</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
+        <v>0.749</v>
+      </c>
+      <c r="F7" t="n">
+        <v>17.8216</v>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>调出目标(排名下降)</t>
@@ -650,17 +652,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-02-11 09:30</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>港股红利ETF博时</t>
+          <t>港股通互联网ETF富国</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>sh513690</t>
+          <t>sz159792</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -669,31 +671,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1.185</v>
+        <v>0.907</v>
       </c>
       <c r="F8" t="n">
-        <v>1.4161</v>
+        <v>38.7844</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>动量排名第1/6</t>
+          <t>动量排名第1/39</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-02-13 09:30</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>港股红利ETF博时</t>
+          <t>港股通互联网ETF富国</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>sh513690</t>
+          <t>sz159792</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -702,11 +704,9 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1.161</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.099</v>
-      </c>
+        <v>0.902</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>调出目标(排名下降)</t>
@@ -716,17 +716,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-02-13 09:30</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>中韩半导体ETF华泰柏瑞</t>
+          <t>恒生科技ETF华泰柏瑞</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>sh513310</t>
+          <t>sh513130</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -735,31 +735,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3.603</v>
+        <v>0.764</v>
       </c>
       <c r="F10" t="n">
-        <v>2.5274</v>
+        <v>23.9422</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>动量排名第1/15</t>
+          <t>动量排名第1/39</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-02-26 09:30</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>中韩半导体ETF华泰柏瑞</t>
+          <t>恒生科技ETF华泰柏瑞</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>sh513310</t>
+          <t>sh513130</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -768,29 +768,29 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4.321</v>
+        <v>0.744</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>调出目标(排名下降)</t>
+          <t>盈利保护</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-02-26 09:30</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>日经ETF华夏</t>
+          <t>港股红利ETF博时</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>sh513520</t>
+          <t>sh513690</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -799,31 +799,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2.123</v>
+        <v>0.91</v>
       </c>
       <c r="F12" t="n">
-        <v>3.3537</v>
+        <v>0.9121</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>动量排名第1/18</t>
+          <t>动量排名第1/39</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-02-27 09:30</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>日经ETF华夏</t>
+          <t>港股红利ETF博时</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>sh513520</t>
+          <t>sh513690</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2.128</v>
+        <v>0.927</v>
       </c>
       <c r="F13" t="n">
-        <v>3.8318</v>
+        <v>0.9442</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -846,17 +846,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-02-27 09:30</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>中韩半导体ETF华泰柏瑞</t>
+          <t>港股通互联网ETF富国</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>sh513310</t>
+          <t>sz159792</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -865,31 +865,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4.256</v>
+        <v>0.917</v>
       </c>
       <c r="F14" t="n">
-        <v>11.0234</v>
+        <v>9.997</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>动量排名第1/18</t>
+          <t>动量排名第1/39</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-02 09:30</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>中韩半导体ETF华泰柏瑞</t>
+          <t>港股通互联网ETF富国</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>sh513310</t>
+          <t>sz159792</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -898,29 +898,29 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4.103</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>盈利保护(回撤超5%)</t>
+          <t>盈利保护</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-02 09:30</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>南方原油LOF</t>
+          <t>恒生科技ETF华泰柏瑞</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>sh501018</t>
+          <t>sh513130</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -929,31 +929,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1.583</v>
+        <v>0.793</v>
       </c>
       <c r="F16" t="n">
-        <v>7.7257</v>
+        <v>3.9558</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>动量排名第1/17</t>
+          <t>动量排名第1/39</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-04 09:30</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>南方原油LOF</t>
+          <t>恒生科技ETF华泰柏瑞</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>sh501018</t>
+          <t>sh513130</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -962,9 +962,11 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="F17" t="inlineStr"/>
+        <v>0.795</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3.1375</v>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>调出目标(排名下降)</t>
@@ -974,17 +976,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-04 09:30</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>豆粕ETF华夏</t>
+          <t>港股红利ETF博时</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>sz159985</t>
+          <t>sh513690</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -993,31 +995,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2.102</v>
+        <v>0.944</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5382</v>
+        <v>1.1244</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>动量排名第1/7</t>
+          <t>动量排名第1/39</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-05 09:30</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>豆粕ETF华夏</t>
+          <t>港股红利ETF博时</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>sz159985</t>
+          <t>sh513690</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1026,10 +1028,10 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2.061</v>
+        <v>0.954</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5197000000000001</v>
+        <v>1.1062</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1040,17 +1042,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-05 09:30</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>中韩半导体ETF华泰柏瑞</t>
+          <t>港股通互联网ETF富国</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>sh513310</t>
+          <t>sz159792</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1059,31 +1061,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4.099</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>5.5332</v>
+        <v>1.1716</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>动量排名第1/10</t>
+          <t>动量排名第1/39</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-09 09:30</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>中韩半导体ETF华泰柏瑞</t>
+          <t>港股通互联网ETF富国</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>sh513310</t>
+          <t>sz159792</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1092,9 +1094,11 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3.995</v>
-      </c>
-      <c r="F21" t="inlineStr"/>
+        <v>0.9409999999999999</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.8744</v>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
           <t>调出目标(排名下降)</t>
@@ -1104,17 +1108,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-10 09:30</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>自由现金流ETF华夏</t>
+          <t>港股红利ETF博时</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>sz159201</t>
+          <t>sh513690</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1123,31 +1127,31 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1.389</v>
+        <v>0.962</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8129999999999999</v>
+        <v>1.1518</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>动量排名第1/6</t>
+          <t>动量排名第1/39</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-11 09:30</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>自由现金流ETF华夏</t>
+          <t>港股红利ETF博时</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>sz159201</t>
+          <t>sh513690</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1156,10 +1160,10 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1.401</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9365</v>
+        <v>0.5636</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1170,17 +1174,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-11 09:30</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>豆粕ETF华夏</t>
+          <t>有色ETF大成</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>sz159985</t>
+          <t>sz159980</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1189,31 +1193,31 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2.244</v>
+        <v>1.753</v>
       </c>
       <c r="F24" t="n">
-        <v>2.2449</v>
+        <v>0.5959</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>动量排名第1/9</t>
+          <t>动量排名第1/39</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-12 09:30</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>豆粕ETF华夏</t>
+          <t>有色ETF大成</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>sz159985</t>
+          <t>sz159980</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1222,10 +1226,10 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2.232</v>
+        <v>1.757</v>
       </c>
       <c r="F25" t="n">
-        <v>2.7265</v>
+        <v>0.6189</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1236,17 +1240,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-12 09:30</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>南方原油LOF</t>
+          <t>德国ETF华安</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>sh501018</t>
+          <t>sh513030</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1255,31 +1259,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1.731</v>
+        <v>1.795</v>
       </c>
       <c r="F26" t="n">
-        <v>20.8388</v>
+        <v>0.8084</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>动量排名第1/11</t>
+          <t>动量排名第1/39</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-16 09:30</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>南方原油LOF</t>
+          <t>德国ETF华安</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>sh501018</t>
+          <t>sh513030</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1288,9 +1292,11 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="F27" t="inlineStr"/>
+        <v>1.75</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.6324</v>
+      </c>
       <c r="G27" t="inlineStr">
         <is>
           <t>调出目标(排名下降)</t>
@@ -1300,17 +1306,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-16 09:30</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>能源化工ETF建信</t>
+          <t>黄金ETF华安</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>sz159981</t>
+          <t>sh518880</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1319,31 +1325,31 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1.652</v>
+        <v>6.938</v>
       </c>
       <c r="F28" t="n">
-        <v>22.2895</v>
+        <v>0.731</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>动量排名第1/8</t>
+          <t>动量排名第1/39</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-24 09:30</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>能源化工ETF建信</t>
+          <t>黄金ETF华安</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>sz159981</t>
+          <t>sh518880</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1352,7 +1358,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1.72</v>
+        <v>7.012</v>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
@@ -1364,17 +1370,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-24 09:30</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>城投债ETF海富通</t>
+          <t>白银LOF国投</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>sz511220</t>
+          <t>sz161226</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1383,31 +1389,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>10.295</v>
+        <v>0.995</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0256</v>
+        <v>0.7812</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>动量排名第1/2</t>
+          <t>动量排名第1/39</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-25 09:30</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>城投债ETF海富通</t>
+          <t>白银LOF国投</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>sz511220</t>
+          <t>sz161226</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1416,10 +1422,10 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>10.301</v>
+        <v>0.982</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0276</v>
+        <v>0.851</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1430,17 +1436,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-25 09:30</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>创业板成长ETF华夏</t>
+          <t>黄金ETF华安</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>sz159967</t>
+          <t>sh518880</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1449,31 +1455,31 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.656</v>
+        <v>7.029</v>
       </c>
       <c r="F32" t="n">
-        <v>0.5697</v>
+        <v>1.3885</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>动量排名第1/2</t>
+          <t>动量排名第1/39</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-27 09:30</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>创业板成长ETF华夏</t>
+          <t>黄金ETF华安</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>sz159967</t>
+          <t>sh518880</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1482,7 +1488,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.647</v>
+        <v>6.877</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
@@ -1494,17 +1500,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-30 09:30</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>能源化工ETF建信</t>
+          <t>黄金ETF华安</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>sz159981</t>
+          <t>sh518880</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1513,31 +1519,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1.774</v>
+        <v>7.164</v>
       </c>
       <c r="F34" t="n">
-        <v>19.6379</v>
+        <v>1.2484</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>动量排名第1/3</t>
+          <t>动量排名第1/39</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-31 09:30</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>能源化工ETF建信</t>
+          <t>黄金ETF华安</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>sz159981</t>
+          <t>sh518880</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1546,29 +1552,29 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1.72</v>
+        <v>7.982</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>盈利保护(回撤超5%)</t>
+          <t>调出目标(排名下降)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-31 09:30</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>城投债ETF海富通</t>
+          <t>红利低波ETF华泰柏瑞</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>sz511220</t>
+          <t>sh512890</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1577,31 +1583,31 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>10.312</v>
+        <v>1.116</v>
       </c>
       <c r="F36" t="n">
-        <v>0.0389</v>
+        <v>0.0007</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>动量排名第1/1</t>
+          <t>动量排名第1/39</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-03 09:30</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>城投债ETF海富通</t>
+          <t>红利低波ETF华泰柏瑞</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>sz511220</t>
+          <t>sh512890</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1610,10 +1616,10 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>10.321</v>
+        <v>1.13</v>
       </c>
       <c r="F37" t="n">
-        <v>0.0399</v>
+        <v>0.0278</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1624,17 +1630,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-03 09:30</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>南方原油LOF</t>
+          <t>黄金ETF华安</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>sh501018</t>
+          <t>sh518880</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1643,31 +1649,31 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2.393</v>
+        <v>7.465</v>
       </c>
       <c r="F38" t="n">
-        <v>88.34739999999999</v>
+        <v>2.429</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>动量排名第1/3</t>
+          <t>动量排名第1/39</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-07 09:30</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>南方原油LOF</t>
+          <t>黄金ETF华安</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>sh501018</t>
+          <t>sh518880</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1676,7 +1682,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2.584</v>
+        <v>7.471</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
@@ -1688,17 +1694,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-07 09:30</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>能源化工ETF建信</t>
+          <t>德国ETF华安</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>sz159981</t>
+          <t>sh513030</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1710,28 +1716,28 @@
         <v>1.786</v>
       </c>
       <c r="F40" t="n">
-        <v>3.3486</v>
+        <v>0.0675</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>动量排名第1/2</t>
+          <t>动量排名第1/39</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-08 09:30</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>能源化工ETF建信</t>
+          <t>德国ETF华安</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>sz159981</t>
+          <t>sh513030</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1740,29 +1746,29 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1.64</v>
+        <v>1.848</v>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>盈利保护(回撤超5%)</t>
+          <t>调出目标(排名下降)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-08 09:30</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>创业板成长ETF华夏</t>
+          <t>黄金ETF华安</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>sz159967</t>
+          <t>sh518880</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1771,31 +1777,31 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.6820000000000001</v>
+        <v>7.612</v>
       </c>
       <c r="F42" t="n">
-        <v>0.1925</v>
+        <v>1.4218</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>动量排名第1/2</t>
+          <t>动量排名第1/39</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-24 09:30</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>创业板成长ETF华夏</t>
+          <t>黄金ETF华安</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>sz159967</t>
+          <t>sh518880</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1804,29 +1810,29 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.777</v>
+        <v>7.557</v>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>盈利保护(回撤超5%)</t>
+          <t>调出目标(排名下降)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-04-24 09:30</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>纳指科技ETF景顺</t>
+          <t>德国ETF华安</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>sz159509</t>
+          <t>sh513030</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1835,31 +1841,31 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2.296</v>
+        <v>1.848</v>
       </c>
       <c r="F44" t="n">
-        <v>6.3906</v>
+        <v>1.4882</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>动量排名第1/29</t>
+          <t>动量排名第1/39</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-04-27 09:30</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>纳指科技ETF景顺</t>
+          <t>德国ETF华安</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>sz159509</t>
+          <t>sh513030</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1868,11 +1874,9 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="F45" t="n">
-        <v>8.453099999999999</v>
-      </c>
+        <v>1.868</v>
+      </c>
+      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
           <t>调出目标(排名下降)</t>
@@ -1882,17 +1886,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-04-27 09:30</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>创业板成长ETF华夏</t>
+          <t>东南亚科技ETF华泰柏瑞</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>sz159967</t>
+          <t>sh513730</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1901,31 +1905,31 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.776</v>
+        <v>1.204</v>
       </c>
       <c r="F46" t="n">
-        <v>14.4945</v>
+        <v>1.7111</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>动量排名第1/26</t>
+          <t>动量排名第1/39</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-04-30 09:30</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>创业板成长ETF华夏</t>
+          <t>东南亚科技ETF华泰柏瑞</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>sz159967</t>
+          <t>sh513730</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1934,9 +1938,11 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.781</v>
-      </c>
-      <c r="F47" t="inlineStr"/>
+        <v>1.217</v>
+      </c>
+      <c r="F47" t="n">
+        <v>2.6279</v>
+      </c>
       <c r="G47" t="inlineStr">
         <is>
           <t>调出目标(排名下降)</t>
@@ -1946,17 +1952,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-04-30 09:30</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>纳指科技ETF景顺</t>
+          <t>德国ETF华安</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>sz159509</t>
+          <t>sh513030</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1965,31 +1971,31 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2.396</v>
+        <v>1.9</v>
       </c>
       <c r="F48" t="n">
-        <v>9.4405</v>
+        <v>3.3679</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>动量排名第1/21</t>
+          <t>动量排名第1/39</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-06 09:30</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>纳指科技ETF景顺</t>
+          <t>德国ETF华安</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>sz159509</t>
+          <t>sh513030</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1998,9 +2004,11 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2.542</v>
-      </c>
-      <c r="F49" t="inlineStr"/>
+        <v>1.854</v>
+      </c>
+      <c r="F49" t="n">
+        <v>4.4512</v>
+      </c>
       <c r="G49" t="inlineStr">
         <is>
           <t>调出目标(排名下降)</t>
@@ -2010,17 +2018,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-05-06 09:30</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>中韩半导体ETF华泰柏瑞</t>
+          <t>东南亚科技ETF华泰柏瑞</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>sh513310</t>
+          <t>sh513730</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2029,31 +2037,31 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4.72</v>
+        <v>1.237</v>
       </c>
       <c r="F50" t="n">
-        <v>12.1496</v>
+        <v>5.4328</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>动量排名第1/24</t>
+          <t>动量排名第1/39</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-12 09:30</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>中韩半导体ETF华泰柏瑞</t>
+          <t>东南亚科技ETF华泰柏瑞</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>sh513310</t>
+          <t>sh513730</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2062,7 +2070,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5.598</v>
+        <v>1.244</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
@@ -2074,17 +2082,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-05-12 09:30</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>科创50ETF易方达</t>
+          <t>德国ETF华安</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>sh588080</t>
+          <t>sh513030</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2093,31 +2101,31 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1.761</v>
+        <v>1.816</v>
       </c>
       <c r="F52" t="n">
-        <v>20.2438</v>
+        <v>4.1388</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>动量排名第1/25</t>
+          <t>动量排名第1/39</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-05-15 09:30</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>科创50ETF易方达</t>
+          <t>德国ETF华安</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>sh588080</t>
+          <t>sh513030</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2126,29 +2134,29 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1.733</v>
+        <v>1.859</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>盈利保护(回撤超5%)</t>
+          <t>调出目标(排名下降)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-05-15 09:30</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>纳指科技ETF景顺</t>
+          <t>东南亚科技ETF华泰柏瑞</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>sz159509</t>
+          <t>sh513730</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2157,31 +2165,31 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2.554</v>
+        <v>1.242</v>
       </c>
       <c r="F54" t="n">
-        <v>7.9397</v>
+        <v>6.376</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>动量排名第1/16</t>
+          <t>动量排名第1/39</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-05-18 09:30</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>纳指科技ETF景顺</t>
+          <t>东南亚科技ETF华泰柏瑞</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>sz159509</t>
+          <t>sh513730</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2190,10 +2198,10 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2.482</v>
+        <v>1.21</v>
       </c>
       <c r="F55" t="n">
-        <v>5.1497</v>
+        <v>3.0156</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2204,17 +2212,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-05-18 09:30</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>科创50ETF易方达</t>
+          <t>纳指科技ETF景顺</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>sh588080</t>
+          <t>sz159509</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2223,31 +2231,31 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1.747</v>
+        <v>1.504</v>
       </c>
       <c r="F56" t="n">
-        <v>14.8972</v>
+        <v>3.2144</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>动量排名第1/16</t>
+          <t>动量排名第1/39</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-05-21 09:30</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>科创50ETF易方达</t>
+          <t>纳指科技ETF景顺</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>sh588080</t>
+          <t>sz159509</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2256,7 +2264,7 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1.804</v>
+        <v>1.539</v>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
@@ -2268,17 +2276,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-05-21 09:30</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>纳指科技ETF景顺</t>
+          <t>纳指ETF国泰</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>sz159509</t>
+          <t>sh513100</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2287,31 +2295,31 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2.562</v>
+        <v>1.568</v>
       </c>
       <c r="F58" t="n">
-        <v>2.6446</v>
+        <v>2.0291</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>动量排名第1/6</t>
+          <t>动量排名第1/39</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-05-25 09:30</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>纳指科技ETF景顺</t>
+          <t>纳指ETF国泰</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>sz159509</t>
+          <t>sh513100</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2320,10 +2328,10 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2.703</v>
+        <v>1.589</v>
       </c>
       <c r="F59" t="n">
-        <v>3.2438</v>
+        <v>1.9437</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2334,17 +2342,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-05-25 09:30</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>科创50ETF易方达</t>
+          <t>纳指科技ETF景顺</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>sh588080</t>
+          <t>sz159509</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2353,31 +2361,31 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1.936</v>
+        <v>1.571</v>
       </c>
       <c r="F60" t="n">
-        <v>18.0984</v>
+        <v>2.5755</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>动量排名第1/11</t>
+          <t>动量排名第1/39</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-05-27 09:30</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>科创50ETF易方达</t>
+          <t>纳指科技ETF景顺</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>sh588080</t>
+          <t>sz159509</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2386,31 +2394,31 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1.857</v>
+        <v>1.564</v>
       </c>
       <c r="F61" t="n">
-        <v>12.2032</v>
+        <v>0.8737</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>盈利保护(回撤超5%)</t>
+          <t>调出目标(排名下降)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-05-27 09:30</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>中韩半导体ETF华泰柏瑞</t>
+          <t>白银LOF国投</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>sh513310</t>
+          <t>sz161226</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2419,31 +2427,31 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6.498</v>
+        <v>1.044</v>
       </c>
       <c r="F62" t="n">
-        <v>144.6758</v>
+        <v>1.1686</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>动量排名第1/38</t>
+          <t>动量排名第1/39</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-05-28 09:30</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>中韩半导体ETF华泰柏瑞</t>
+          <t>白银LOF国投</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>sh513310</t>
+          <t>sz161226</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2452,31 +2460,29 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6.051</v>
-      </c>
-      <c r="F63" t="n">
-        <v>112.3247</v>
-      </c>
+        <v>1.004</v>
+      </c>
+      <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>盈利保护(回撤超5%, 日内跌-6.88%)</t>
+          <t>调出目标(排名下降)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-05-28 09:30</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>科创50ETF易方达</t>
+          <t>中韩半导体ETF华泰柏瑞</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>sh588080</t>
+          <t>sh513310</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2485,31 +2491,31 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1.877</v>
+        <v>1.598</v>
       </c>
       <c r="F64" t="n">
-        <v>12.7574</v>
+        <v>0.8518</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>动量排名第1/38</t>
+          <t>动量排名第1/39</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-05-29 09:33</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>科创50ETF易方达</t>
+          <t>中韩半导体ETF华泰柏瑞</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>sh588080</t>
+          <t>sh513310</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2518,47 +2524,4849 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1.822</v>
-      </c>
-      <c r="F65" t="n">
-        <v>11.2327</v>
-      </c>
+        <v>1.587</v>
+      </c>
+      <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>盈利保护(回撤超5%)</t>
+          <t>调出目标(排名下降)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-05-29 09:33</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
+          <t>能源化工ETF建信</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>sz159981</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>1.397</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0.7012</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>能源化工ETF建信</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>sz159981</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>1.335</v>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>盈利保护</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>中韩半导体ETF华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>sh513310</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>1.644</v>
+      </c>
+      <c r="F68" t="n">
+        <v>1.0866</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>中韩半导体ETF华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>sh513310</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>1.627</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.8381999999999999</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>调出目标(排名下降)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>纳指科技ETF景顺</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>sz159509</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>1.662</v>
+      </c>
+      <c r="F70" t="n">
+        <v>1.0115</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>纳指科技ETF景顺</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>sz159509</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>1.725</v>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>调出目标(排名下降)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>创业板ETF易方达</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>sz159915</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>2.212</v>
+      </c>
+      <c r="F72" t="n">
+        <v>1.4538</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>创业板ETF易方达</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>sz159915</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>2.206</v>
+      </c>
+      <c r="F73" t="n">
+        <v>1.5211</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>调出目标(排名下降)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>纳指科技ETF景顺</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>sz159509</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>1.715</v>
+      </c>
+      <c r="F74" t="n">
+        <v>2.1032</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>纳指科技ETF景顺</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>sz159509</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>1.758</v>
+      </c>
+      <c r="F75" t="n">
+        <v>2.4957</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>调出目标(排名下降)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>创业板ETF易方达</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>sz159915</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>2.318</v>
+      </c>
+      <c r="F76" t="n">
+        <v>2.6687</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>创业板ETF易方达</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>sz159915</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>2.336</v>
+      </c>
+      <c r="F77" t="n">
+        <v>1.5315</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>调出目标(排名下降)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>机器人ETF华夏</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>sh562500</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>0.948</v>
+      </c>
+      <c r="F78" t="n">
+        <v>1.804</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>机器人ETF华夏</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>sh562500</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>0.997</v>
+      </c>
+      <c r="F79" t="n">
+        <v>2.5589</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>调出目标(排名下降)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
           <t>创业板成长ETF华夏</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>sz159967</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>买入</t>
-        </is>
-      </c>
-      <c r="E66" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F66" t="n">
-        <v>5.0321</v>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>动量排名第1/38</t>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>0.534</v>
+      </c>
+      <c r="F80" t="n">
+        <v>2.8919</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>创业板成长ETF华夏</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>sz159967</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="F81" t="n">
+        <v>5.2561</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>调出目标(排名下降)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>科创50ETF易方达</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>sh588080</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>1.305</v>
+      </c>
+      <c r="F82" t="n">
+        <v>5.3949</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>科创50ETF易方达</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>sh588080</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>1.252</v>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>盈利保护</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>A500ETF华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>sh563360</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>1.158</v>
+      </c>
+      <c r="F84" t="n">
+        <v>2.2554</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>A500ETF华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>sh563360</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>1.184</v>
+      </c>
+      <c r="F85" t="n">
+        <v>1.6871</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>调出目标(排名下降)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>创业板ETF易方达</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>sz159915</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>2.845</v>
+      </c>
+      <c r="F86" t="n">
+        <v>9.6075</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>创业板ETF易方达</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>sz159915</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>3.062</v>
+      </c>
+      <c r="F87" t="n">
+        <v>5.197</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>调出目标(排名下降)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>中韩半导体ETF华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>sh513310</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>2.165</v>
+      </c>
+      <c r="F88" t="n">
+        <v>5.5134</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>中韩半导体ETF华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>sh513310</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>盈利保护</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>白银LOF国投</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>sz161226</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>1.286</v>
+      </c>
+      <c r="F90" t="n">
+        <v>3.4003</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>白银LOF国投</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>sz161226</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>1.356</v>
+      </c>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>调出目标(排名下降)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>纳指科技ETF景顺</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>sz159509</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>2.025</v>
+      </c>
+      <c r="F92" t="n">
+        <v>2.8357</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>纳指科技ETF景顺</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>sz159509</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>2.086</v>
+      </c>
+      <c r="F93" t="n">
+        <v>2.6451</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>调出目标(排名下降)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>黄金ETF华安</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>sh518880</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>9.186999999999999</v>
+      </c>
+      <c r="F94" t="n">
+        <v>3.2438</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>黄金ETF华安</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>sh518880</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>9.244</v>
+      </c>
+      <c r="F95" t="n">
+        <v>4.0266</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>调出目标(排名下降)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>白银LOF国投</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>sz161226</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>1.446</v>
+      </c>
+      <c r="F96" t="n">
+        <v>10.4255</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>白银LOF国投</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>sz161226</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>1.367</v>
+      </c>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>盈利保护</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>中韩半导体ETF华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>sh513310</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>2.385</v>
+      </c>
+      <c r="F98" t="n">
+        <v>6.5246</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>中韩半导体ETF华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>sh513310</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>2.386</v>
+      </c>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>调出目标(排名下降)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>纳指科技ETF景顺</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>sz159509</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>2.203</v>
+      </c>
+      <c r="F100" t="n">
+        <v>3.0717</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>纳指科技ETF景顺</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>sz159509</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="F101" t="n">
+        <v>3.5819</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>调出目标(排名下降)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>黄金ETF华安</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>sh518880</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>8.914</v>
+      </c>
+      <c r="F102" t="n">
+        <v>3.9628</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>黄金ETF华安</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>sh518880</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>8.597</v>
+      </c>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>调出目标(排名下降)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>日经ETF华夏</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>sh513520</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>1.935</v>
+      </c>
+      <c r="F104" t="n">
+        <v>4.3153</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>日经ETF华夏</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>sh513520</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>1.993</v>
+      </c>
+      <c r="F105" t="n">
+        <v>6.2327</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>调出目标(排名下降)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>中韩半导体ETF华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>sh513310</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>2.831</v>
+      </c>
+      <c r="F106" t="n">
+        <v>6.9064</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>中韩半导体ETF华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>sh513310</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>2.684</v>
+      </c>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>盈利保护</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>纳指科技ETF景顺</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>sz159509</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>2.228</v>
+      </c>
+      <c r="F108" t="n">
+        <v>2.8692</v>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>纳指科技ETF景顺</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>sz159509</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>2.244</v>
+      </c>
+      <c r="F109" t="n">
+        <v>1.8256</v>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>调出目标(排名下降)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>日经ETF华夏</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>sh513520</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="F110" t="n">
+        <v>3.075</v>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>日经ETF华夏</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>sh513520</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>1.967</v>
+      </c>
+      <c r="F111" t="n">
+        <v>2.6762</v>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>调出目标(排名下降)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>中韩半导体ETF华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>sh513310</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>2.695</v>
+      </c>
+      <c r="F112" t="n">
+        <v>4.7302</v>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>中韩半导体ETF华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>sh513310</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>调出目标(排名下降)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>纳指生物科技ETF汇添富</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>sh513290</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>1.478</v>
+      </c>
+      <c r="F114" t="n">
+        <v>1.8197</v>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>纳指生物科技ETF汇添富</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>sh513290</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>调出目标(排名下降)</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>港股红利ETF博时</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>sh513690</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>1.146</v>
+      </c>
+      <c r="F116" t="n">
+        <v>0.8172</v>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>港股红利ETF博时</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>sh513690</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>1.137</v>
+      </c>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>调出目标(排名下降)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>红利低波ETF华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>sh512890</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>1.228</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.3341</v>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>红利低波ETF华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>sh512890</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>1.209</v>
+      </c>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>调出目标(排名下降)</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>纳指生物科技ETF汇添富</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>sh513290</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>1.457</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1.2808</v>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>纳指生物科技ETF汇添富</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>sh513290</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>1.592</v>
+      </c>
+      <c r="F121" t="n">
+        <v>2.5594</v>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>调出目标(排名下降)</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>白银LOF国投</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>sz161226</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>1.617</v>
+      </c>
+      <c r="F122" t="n">
+        <v>3.4094</v>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>白银LOF国投</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>sz161226</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>1.937</v>
+      </c>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>调出目标(排名下降)</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>有色ETF大成</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>sz159980</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>1.892</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.6083</v>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>有色ETF大成</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>sz159980</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>1.932</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.7729</v>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>调出目标(排名下降)</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>创业板成长ETF华夏</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>sz159967</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="F126" t="n">
+        <v>1.0225</v>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>创业板成长ETF华夏</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>sz159967</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>0.624</v>
+      </c>
+      <c r="F127" t="n">
+        <v>1.4841</v>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>调出目标(排名下降)</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>白银LOF国投</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>sz161226</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>2.016</v>
+      </c>
+      <c r="F128" t="n">
+        <v>63.6628</v>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>白银LOF国投</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>sz161226</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>2.027</v>
+      </c>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>调出目标(排名下降)</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>创业板成长ETF华夏</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>sz159967</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="F130" t="n">
+        <v>1.5246</v>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>创业板成长ETF华夏</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>sz159967</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>0.617</v>
+      </c>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>调出目标(排名下降)</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>有色ETF大成</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>sz159980</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>1.899</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.7917999999999999</v>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2025-12-23</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>有色ETF大成</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>sz159980</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>1.932</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.987</v>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>调出目标(排名下降)</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2025-12-23</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>创业板成长ETF华夏</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>sz159967</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>0.648</v>
+      </c>
+      <c r="F134" t="n">
+        <v>2.2692</v>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>创业板成长ETF华夏</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>sz159967</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>调出目标(排名下降)</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>有色ETF大成</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>sz159980</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>1.996</v>
+      </c>
+      <c r="F136" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>有色ETF大成</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>sz159980</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>2.126</v>
+      </c>
+      <c r="F137" t="n">
+        <v>2.0212</v>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>调出目标(排名下降)</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>中韩半导体ETF华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>sh513310</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>3.126</v>
+      </c>
+      <c r="F138" t="n">
+        <v>2.0291</v>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>中韩半导体ETF华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>sh513310</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>3.011</v>
+      </c>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>盈利保护</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>有色ETF大成</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>sz159980</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>2.073</v>
+      </c>
+      <c r="F140" t="n">
+        <v>2.1327</v>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>有色ETF大成</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>sz159980</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>2.086</v>
+      </c>
+      <c r="F141" t="n">
+        <v>2.2378</v>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>调出目标(排名下降)</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>中证500ETF南方</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>sh510500</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>8.215999999999999</v>
+      </c>
+      <c r="F142" t="n">
+        <v>2.5642</v>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>中证500ETF南方</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>sh510500</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>8.305999999999999</v>
+      </c>
+      <c r="F143" t="n">
+        <v>3.7771</v>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>调出目标(排名下降)</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>中韩半导体ETF华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>sh513310</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>3.001</v>
+      </c>
+      <c r="F144" t="n">
+        <v>10.3422</v>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>中韩半导体ETF华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>sh513310</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>3.363</v>
+      </c>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>调出目标(排名下降)</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>科创50ETF易方达</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>sh588080</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>1.587</v>
+      </c>
+      <c r="F146" t="n">
+        <v>4.2645</v>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>科创50ETF易方达</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>sh588080</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>1.583</v>
+      </c>
+      <c r="F147" t="n">
+        <v>3.8753</v>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>调出目标(排名下降)</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>中韩半导体ETF华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>sh513310</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>3.613</v>
+      </c>
+      <c r="F148" t="n">
+        <v>21.1511</v>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>中韩半导体ETF华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>sh513310</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>3.365</v>
+      </c>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>盈利保护</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>港股红利ETF博时</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>sh513690</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>1.114</v>
+      </c>
+      <c r="F150" t="n">
+        <v>0.6293</v>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>港股红利ETF博时</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>sh513690</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>1.137</v>
+      </c>
+      <c r="F151" t="n">
+        <v>0.6922</v>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>调出目标(排名下降)</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>中证2000ETF华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>sh563300</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>1.491</v>
+      </c>
+      <c r="F152" t="n">
+        <v>0.8252</v>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>中证2000ETF华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>sh563300</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>1.493</v>
+      </c>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>调出目标(排名下降)</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>港股红利ETF博时</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>sh513690</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>1.167</v>
+      </c>
+      <c r="F154" t="n">
+        <v>0.8957000000000001</v>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>港股红利ETF博时</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>sh513690</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>1.166</v>
+      </c>
+      <c r="F155" t="n">
+        <v>1.1034</v>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>调出目标(排名下降)</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>南方原油LOF</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>sh501018</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>1.314</v>
+      </c>
+      <c r="F156" t="n">
+        <v>3.522</v>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>南方原油LOF</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>sh501018</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>1.395</v>
+      </c>
+      <c r="F157" t="n">
+        <v>4.2621</v>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>调出目标(排名下降)</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>中韩半导体ETF华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>sh513310</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>3.489</v>
+      </c>
+      <c r="F158" t="n">
+        <v>4.5454</v>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>中韩半导体ETF华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>sh513310</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>3.422</v>
+      </c>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>调出目标(排名下降)</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>港股红利ETF博时</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>sh513690</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>1.185</v>
+      </c>
+      <c r="F160" t="n">
+        <v>1.3017</v>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>港股红利ETF博时</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>sh513690</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>1.181</v>
+      </c>
+      <c r="F161" t="n">
+        <v>1.2493</v>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>调出目标(排名下降)</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>日经ETF华夏</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>sh513520</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>2.105</v>
+      </c>
+      <c r="F162" t="n">
+        <v>1.6155</v>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>日经ETF华夏</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>sh513520</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>2.141</v>
+      </c>
+      <c r="F163" t="n">
+        <v>2.2425</v>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>调出目标(排名下降)</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>中韩半导体ETF华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>sh513310</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>3.941</v>
+      </c>
+      <c r="F164" t="n">
+        <v>4.3908</v>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>中韩半导体ETF华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>sh513310</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>4.321</v>
+      </c>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>调出目标(排名下降)</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>中韩半导体ETF华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>sh513310</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>4.256</v>
+      </c>
+      <c r="F166" t="n">
+        <v>8.790699999999999</v>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>中韩半导体ETF华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>sh513310</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>4.103</v>
+      </c>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>盈利保护</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>日经ETF华夏</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>sh513520</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>2.117</v>
+      </c>
+      <c r="F168" t="n">
+        <v>3.7415</v>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>日经ETF华夏</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>sh513520</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>1.998</v>
+      </c>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>盈利保护</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>港股红利ETF博时</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>sh513690</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>1.191</v>
+      </c>
+      <c r="F170" t="n">
+        <v>0.9923999999999999</v>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>港股红利ETF博时</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>sh513690</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>1.167</v>
+      </c>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>调出目标(排名下降)</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>自由现金流ETF华夏</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>sz159201</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>1.372</v>
+      </c>
+      <c r="F172" t="n">
+        <v>0.4634</v>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>自由现金流ETF华夏</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>sz159201</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>1.391</v>
+      </c>
+      <c r="F173" t="n">
+        <v>0.5813</v>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>调出目标(排名下降)</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>豆粕ETF华夏</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>sz159985</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>2.126</v>
+      </c>
+      <c r="F174" t="n">
+        <v>0.6143999999999999</v>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>豆粕ETF华夏</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>sz159985</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>2.232</v>
+      </c>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>调出目标(排名下降)</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>能源化工ETF建信</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>sz159981</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>1.592</v>
+      </c>
+      <c r="F176" t="n">
+        <v>1.2006</v>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>能源化工ETF建信</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>sz159981</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>1.477</v>
+      </c>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>盈利保护</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>自由现金流ETF华夏</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>sz159201</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E178" t="n">
+        <v>1.389</v>
+      </c>
+      <c r="F178" t="n">
+        <v>0.7325</v>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>自由现金流ETF华夏</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>sz159201</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>1.401</v>
+      </c>
+      <c r="F179" t="n">
+        <v>0.8705000000000001</v>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>调出目标(排名下降)</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>豆粕ETF华夏</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>sz159985</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E180" t="n">
+        <v>2.244</v>
+      </c>
+      <c r="F180" t="n">
+        <v>1.7056</v>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>豆粕ETF华夏</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>sz159985</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>2.321</v>
+      </c>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>调出目标(排名下降)</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>南方原油LOF</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>sh501018</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>1.791</v>
+      </c>
+      <c r="F182" t="n">
+        <v>23.5837</v>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>南方原油LOF</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>sh501018</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>调出目标(排名下降)</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>能源化工ETF建信</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>sz159981</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>1.652</v>
+      </c>
+      <c r="F184" t="n">
+        <v>16.7396</v>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>能源化工ETF建信</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>sz159981</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>调出目标(排名下降)</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>豆粕ETF华夏</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>sz159985</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>2.242</v>
+      </c>
+      <c r="F186" t="n">
+        <v>3.1064</v>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>豆粕ETF华夏</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>sz159985</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>2.159</v>
+      </c>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>盈利保护</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>城投债ETF海富通</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>sz511220</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>10.301</v>
+      </c>
+      <c r="F188" t="n">
+        <v>0.0277</v>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>城投债ETF海富通</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>sz511220</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E189" t="n">
+        <v>10.309</v>
+      </c>
+      <c r="F189" t="n">
+        <v>0.0294</v>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>调出目标(排名下降)</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>创业板成长ETF华夏</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>sz159967</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E190" t="n">
+        <v>0.648</v>
+      </c>
+      <c r="F190" t="n">
+        <v>0.5056</v>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>创业板成长ETF华夏</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>sz159967</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E191" t="n">
+        <v>0.644</v>
+      </c>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>调出目标(排名下降)</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>能源化工ETF建信</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>sz159981</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E192" t="n">
+        <v>1.774</v>
+      </c>
+      <c r="F192" t="n">
+        <v>23.1235</v>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>能源化工ETF建信</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>sz159981</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E193" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>盈利保护</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>城投债ETF海富通</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>sz511220</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E194" t="n">
+        <v>10.312</v>
+      </c>
+      <c r="F194" t="n">
+        <v>0.0369</v>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>城投债ETF海富通</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>sz511220</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E195" t="n">
+        <v>10.326</v>
+      </c>
+      <c r="F195" t="n">
+        <v>0.0409</v>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>调出目标(排名下降)</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>能源化工ETF建信</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>sz159981</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E196" t="n">
+        <v>1.786</v>
+      </c>
+      <c r="F196" t="n">
+        <v>3.9883</v>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>能源化工ETF建信</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>sz159981</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E197" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>盈利保护</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>创业板成长ETF华夏</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>sz159967</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E198" t="n">
+        <v>0.6820000000000001</v>
+      </c>
+      <c r="F198" t="n">
+        <v>0.1118</v>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>创业板成长ETF华夏</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>sz159967</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E199" t="n">
+        <v>0.777</v>
+      </c>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>盈利保护</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>纳指科技ETF景顺</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>sz159509</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E200" t="n">
+        <v>2.296</v>
+      </c>
+      <c r="F200" t="n">
+        <v>5.6809</v>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>纳指科技ETF景顺</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>sz159509</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E201" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="F201" t="n">
+        <v>7.2551</v>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>调出目标(排名下降)</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>创业板成长ETF华夏</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>sz159967</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E202" t="n">
+        <v>0.776</v>
+      </c>
+      <c r="F202" t="n">
+        <v>14.8934</v>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>创业板成长ETF华夏</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>sz159967</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E203" t="n">
+        <v>0.822</v>
+      </c>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>调出目标(排名下降)</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>中韩半导体ETF华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>sh513310</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E204" t="n">
+        <v>5.057</v>
+      </c>
+      <c r="F204" t="n">
+        <v>14.5775</v>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>中韩半导体ETF华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>sh513310</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E205" t="n">
+        <v>5.634</v>
+      </c>
+      <c r="F205" t="inlineStr"/>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>调出目标(排名下降)</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>科创50ETF易方达</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>sh588080</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E206" t="n">
+        <v>1.754</v>
+      </c>
+      <c r="F206" t="n">
+        <v>16.1583</v>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>科创50ETF易方达</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>sh588080</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E207" t="n">
+        <v>1.733</v>
+      </c>
+      <c r="F207" t="inlineStr"/>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>盈利保护</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>纳指科技ETF景顺</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>sz159509</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E208" t="n">
+        <v>2.554</v>
+      </c>
+      <c r="F208" t="n">
+        <v>9.9145</v>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>纳指科技ETF景顺</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>sz159509</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E209" t="n">
+        <v>2.482</v>
+      </c>
+      <c r="F209" t="n">
+        <v>6.9394</v>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>调出目标(排名下降)</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>科创50ETF易方达</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>sh588080</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E210" t="n">
+        <v>1.747</v>
+      </c>
+      <c r="F210" t="n">
+        <v>16.4206</v>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>科创50ETF易方达</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>sh588080</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E211" t="n">
+        <v>1.804</v>
+      </c>
+      <c r="F211" t="inlineStr"/>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>调出目标(排名下降)</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>机器人ETF华夏</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>sh562500</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E212" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="F212" t="n">
+        <v>8.450699999999999</v>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>机器人ETF华夏</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>sh562500</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E213" t="n">
+        <v>1.205</v>
+      </c>
+      <c r="F213" t="n">
+        <v>8.5078</v>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>调出目标(排名下降)</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>科创50ETF易方达</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>sh588080</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E214" t="n">
+        <v>1.913</v>
+      </c>
+      <c r="F214" t="n">
+        <v>17.3555</v>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>动量排名第1/39</t>
         </is>
       </c>
     </row>

--- a/backtest/results_172/七星172_交易记录_2026.xlsx
+++ b/backtest/results_172/七星172_交易记录_2026.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -806,7 +806,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -1720,7 +1720,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -1848,7 +1848,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2108,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -2238,7 +2238,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -2822,7 +2822,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -2888,7 +2888,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -3150,7 +3150,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -3216,7 +3216,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3282,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -3606,7 +3606,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -3670,7 +3670,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -3736,7 +3736,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -3930,7 +3930,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -4126,7 +4126,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -4190,7 +4190,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -4254,7 +4254,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -4318,7 +4318,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -4384,7 +4384,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -4448,7 +4448,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -4644,7 +4644,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -4708,7 +4708,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -4774,7 +4774,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -4968,7 +4968,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -5034,7 +5034,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -5100,7 +5100,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -5164,7 +5164,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -5230,7 +5230,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -5360,7 +5360,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5424,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -5556,7 +5556,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -5620,7 +5620,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -5686,7 +5686,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -5752,7 +5752,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -5816,7 +5816,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -5944,7 +5944,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -6074,7 +6074,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -6202,7 +6202,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -6268,7 +6268,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -6332,7 +6332,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -6396,7 +6396,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -6460,7 +6460,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -6524,7 +6524,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -6590,7 +6590,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -6654,7 +6654,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -6718,7 +6718,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -6784,7 +6784,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -6912,7 +6912,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -7042,7 +7042,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -7236,7 +7236,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -7300,7 +7300,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>动量排名第1/39</t>
+          <t>动量排名第1/40</t>
         </is>
       </c>
     </row>

--- a/backtest/results_172/七星172_交易记录_2026.xlsx
+++ b/backtest/results_172/七星172_交易记录_2026.xlsx
@@ -456,7 +456,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2025-02-13 09:30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -489,7 +489,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>2025-02-14 09:30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -522,7 +522,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>2025-02-14 09:30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -555,7 +555,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-02-17</t>
+          <t>2025-02-17 09:30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -586,7 +586,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-02-17</t>
+          <t>2025-02-17 09:30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -619,7 +619,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2025-02-18 09:30</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -652,7 +652,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-02-19 09:30</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -685,7 +685,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-02-25 09:30</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -716,7 +716,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-02-25 09:30</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -749,7 +749,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-02-28 09:30</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -780,7 +780,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-02-28 09:30</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -813,7 +813,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-03-05 09:30</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -846,7 +846,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-03-05 09:30</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -879,7 +879,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2025-03-10 09:30</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -910,7 +910,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2025-03-10 09:30</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -943,7 +943,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2025-03-11 09:30</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -976,7 +976,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-03-12 09:30</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1009,7 +1009,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
+          <t>2025-03-14 09:30</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1042,7 +1042,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
+          <t>2025-03-14 09:30</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1075,7 +1075,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2025-03-17 09:30</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1108,7 +1108,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2025-03-17 09:30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1141,7 +1141,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-25 09:30</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1174,7 +1174,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-25 09:30</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1207,7 +1207,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-03-26 09:30</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1240,7 +1240,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-03-26 09:30</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1273,7 +1273,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-03-28 09:30</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1306,7 +1306,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-03-28 09:30</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1339,7 +1339,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-03-31 09:30</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1370,7 +1370,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-03-31 09:30</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1403,7 +1403,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2025-04-02 09:30</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1436,7 +1436,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2025-04-02 09:30</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1469,7 +1469,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-07 09:30</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1500,7 +1500,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-04-10 09:30</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1533,7 +1533,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-04-22 09:30</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1564,7 +1564,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-23 09:30</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1597,7 +1597,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-04-28 09:30</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1630,7 +1630,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-04-28 09:30</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1663,7 +1663,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2025-04-30 09:30</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1694,7 +1694,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2025-04-30 09:30</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1727,7 +1727,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-06 09:30</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1758,7 +1758,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-06 09:30</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1791,7 +1791,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-08 09:30</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1822,7 +1822,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-08 09:30</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1855,7 +1855,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-09 09:30</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1886,7 +1886,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-09 09:30</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1919,7 +1919,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-05-12 09:30</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1952,7 +1952,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-05-12 09:30</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1985,7 +1985,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-14 09:30</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2018,7 +2018,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-14 09:30</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2051,7 +2051,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-05-15 09:30</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2082,7 +2082,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-05-15 09:30</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2115,7 +2115,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-05-16 09:30</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2146,7 +2146,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-05-16 09:30</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2179,7 +2179,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-22 09:30</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2212,7 +2212,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-22 09:30</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2245,7 +2245,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-28 09:30</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2276,7 +2276,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-28 09:30</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2309,7 +2309,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-05-29 09:30</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2342,7 +2342,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-05-29 09:30</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2375,7 +2375,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-06-11 09:30</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2408,7 +2408,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-06-11 09:30</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2441,7 +2441,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2025-06-20 09:30</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2472,7 +2472,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2025-06-20 09:30</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2505,7 +2505,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-06-23 09:30</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2536,7 +2536,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-06-23 09:30</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2569,7 +2569,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-06-24 09:30</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2600,7 +2600,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-06-24 09:30</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2633,7 +2633,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-07 09:30</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2666,7 +2666,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-07 09:30</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2699,7 +2699,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-15 09:30</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2730,7 +2730,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-15 09:30</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2763,7 +2763,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-07-16 09:30</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2796,7 +2796,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-07-16 09:30</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2829,7 +2829,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-25 09:30</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2862,7 +2862,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-25 09:30</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2895,7 +2895,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-06 09:30</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2928,7 +2928,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-06 09:30</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2961,7 +2961,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-20 09:30</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2994,7 +2994,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-21 09:30</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3027,7 +3027,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-26 09:30</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3060,7 +3060,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-26 09:30</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3093,7 +3093,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-04 09:30</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3124,7 +3124,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-04 09:30</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3157,7 +3157,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-09 09:30</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3190,7 +3190,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-09 09:30</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3223,7 +3223,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-19 09:30</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3256,7 +3256,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-19 09:30</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3289,7 +3289,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-10-10 09:30</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3320,7 +3320,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-10-10 09:30</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3353,7 +3353,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-14 09:30</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3384,7 +3384,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-14 09:30</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3417,7 +3417,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-15 09:30</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3450,7 +3450,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-15 09:30</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3483,7 +3483,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-16 09:30</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3516,7 +3516,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-16 09:30</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3549,7 +3549,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-20 09:30</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3580,7 +3580,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-20 09:30</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3613,7 +3613,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-23 09:30</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3644,7 +3644,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-23 09:30</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3677,7 +3677,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-27 09:30</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3710,7 +3710,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-27 09:30</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3743,7 +3743,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-10-28 09:30</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3774,7 +3774,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-10-28 09:30</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3807,7 +3807,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-03 09:30</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3840,7 +3840,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-03 09:30</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3873,7 +3873,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-04 09:30</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3904,7 +3904,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-04 09:30</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3937,7 +3937,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-07 09:30</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3970,7 +3970,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-07 09:30</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4003,7 +4003,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-10 09:30</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4036,7 +4036,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-10 09:30</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4069,7 +4069,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-12 09:30</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4100,7 +4100,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-12 09:30</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4133,7 +4133,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-19 09:30</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4164,7 +4164,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-19 09:30</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4197,7 +4197,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-20 09:30</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4228,7 +4228,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-20 09:30</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4261,7 +4261,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-21 09:30</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4292,7 +4292,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-21 09:30</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4325,7 +4325,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-01 09:30</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4358,7 +4358,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-01 09:30</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4391,7 +4391,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-11 09:30</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4422,7 +4422,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-11 09:30</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4455,7 +4455,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-12 09:30</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4488,7 +4488,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-12 09:30</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -4521,7 +4521,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-15 09:30</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -4554,7 +4554,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-15 09:30</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -4587,7 +4587,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-16 09:30</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -4618,7 +4618,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-16 09:30</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -4651,7 +4651,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-18 09:30</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -4682,7 +4682,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-18 09:30</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -4715,7 +4715,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-23 09:30</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -4748,7 +4748,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-23 09:30</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -4781,7 +4781,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-12-31 09:30</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4812,7 +4812,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-12-31 09:30</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4845,7 +4845,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-07 09:30</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -4878,7 +4878,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-07 09:30</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4911,7 +4911,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-08 09:30</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -4942,7 +4942,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-08 09:30</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -4975,7 +4975,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-09 09:30</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5008,7 +5008,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-09 09:30</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5041,7 +5041,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-13 09:30</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5074,7 +5074,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-13 09:30</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -5107,7 +5107,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-27 09:30</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -5138,7 +5138,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-27 09:30</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -5171,7 +5171,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-28 09:30</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -5204,7 +5204,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-28 09:30</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -5237,7 +5237,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-02 09:30</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -5268,7 +5268,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-02 09:30</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -5301,7 +5301,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-03 09:30</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -5334,7 +5334,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-03 09:30</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -5367,7 +5367,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-04 09:30</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -5398,7 +5398,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-04 09:30</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -5431,7 +5431,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-09 09:30</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -5464,7 +5464,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-09 09:30</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -5497,7 +5497,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-10 09:30</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -5530,7 +5530,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-10 09:30</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -5563,7 +5563,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-11 09:30</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -5594,7 +5594,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-11 09:30</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -5627,7 +5627,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-24 09:30</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -5660,7 +5660,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-24 09:30</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -5693,7 +5693,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-25 09:30</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -5726,7 +5726,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-25 09:30</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -5759,7 +5759,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-26 09:30</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -5790,7 +5790,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-27 09:30</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -5823,7 +5823,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-02 09:30</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -5854,7 +5854,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-02 09:30</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -5887,7 +5887,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-03 09:30</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -5918,7 +5918,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-03 09:30</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -5951,7 +5951,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-04 09:30</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5982,7 +5982,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-04 09:30</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -6015,7 +6015,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-06 09:30</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -6048,7 +6048,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-06 09:30</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -6081,7 +6081,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-09 09:30</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -6112,7 +6112,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-09 09:30</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -6145,7 +6145,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-10 09:30</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -6176,7 +6176,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-10 09:30</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -6209,7 +6209,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-11 09:30</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -6242,7 +6242,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-11 09:30</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -6275,7 +6275,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-13 09:30</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -6306,7 +6306,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-13 09:30</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -6339,7 +6339,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-16 09:30</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -6370,7 +6370,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-16 09:30</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -6403,7 +6403,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-24 09:30</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -6434,7 +6434,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-24 09:30</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -6467,7 +6467,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-25 09:30</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -6498,7 +6498,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-25 09:30</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -6531,7 +6531,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-26 09:30</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -6564,7 +6564,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-26 09:30</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -6597,7 +6597,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-30 09:30</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -6628,7 +6628,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-30 09:30</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -6661,7 +6661,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-31 09:30</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -6692,7 +6692,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-31 09:30</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -6725,7 +6725,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-07 09:30</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -6758,7 +6758,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-07 09:30</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -6791,7 +6791,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-08 09:30</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -6822,7 +6822,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-08 09:30</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -6855,7 +6855,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-24 09:30</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -6886,7 +6886,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-24 09:30</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -6919,7 +6919,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-27 09:30</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -6952,7 +6952,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-27 09:30</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -6985,7 +6985,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-07 09:30</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -7016,7 +7016,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-07 09:30</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -7049,7 +7049,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-11 09:30</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -7080,7 +7080,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-11 09:30</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -7113,7 +7113,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-15 09:30</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -7144,7 +7144,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-15 09:30</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -7177,7 +7177,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-18 09:30</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -7210,7 +7210,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-18 09:30</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -7243,7 +7243,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-21 09:30</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -7274,7 +7274,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-21 09:30</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -7307,7 +7307,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-26 09:30</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -7340,7 +7340,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-26 09:30</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">

--- a/backtest/results_172/七星172_交易记录_2026.xlsx
+++ b/backtest/results_172/七星172_交易记录_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H110"/>
+  <dimension ref="A1:H192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -558,14 +558,14 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>7.42%</t>
+          <t>-0.57%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-03-17 13:04</t>
+          <t>2025-02-28 13:04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -584,12 +584,12 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.871</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>调出目标</t>
+          <t>盈利保护</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -597,7 +597,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-03-17 13:04</t>
+          <t>2025-02-28 13:04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -607,16 +607,16 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>港股红利ETF博时</t>
+          <t>恒生ETF华夏</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>sh513690</t>
+          <t>sz159920</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.962</v>
+        <v>1.416</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
@@ -626,14 +626,14 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.08%</t>
+          <t>0.35%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-03-25 13:04</t>
+          <t>2025-03-03 13:04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -643,16 +643,16 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>港股红利ETF博时</t>
+          <t>恒生ETF华夏</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>sh513690</t>
+          <t>sz159920</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.9419999999999999</v>
+        <v>1.421</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
@@ -665,7 +665,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-03-25 13:04</t>
+          <t>2025-03-03 13:04</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -675,16 +675,16 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>有色ETF大成</t>
+          <t>港股通互联网ETF富国</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>sz159980</t>
+          <t>sz159792</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1.753</v>
+        <v>0.876</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
@@ -694,14 +694,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.23%</t>
+          <t>7.53%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-03-26 13:04</t>
+          <t>2025-03-10 13:04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -711,21 +711,21 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>有色ETF大成</t>
+          <t>港股通互联网ETF富国</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>sz159980</t>
+          <t>sz159792</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1.757</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>调出目标</t>
+          <t>盈利保护</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -733,7 +733,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-03-26 13:04</t>
+          <t>2025-03-10 13:04</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -743,16 +743,16 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>德国ETF华安</t>
+          <t>恒生科技ETF华泰柏瑞</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>sh513030</t>
+          <t>sh513130</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.795</v>
+        <v>0.793</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
@@ -762,14 +762,14 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.51%</t>
+          <t>0.25%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-03-28 13:04</t>
+          <t>2025-03-11 13:04</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -779,16 +779,16 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>德国ETF华安</t>
+          <t>恒生科技ETF华泰柏瑞</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>sh513030</t>
+          <t>sh513130</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.75</v>
+        <v>0.795</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
@@ -801,7 +801,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-03-28 13:04</t>
+          <t>2025-03-11 13:04</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -811,16 +811,16 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>黄金ETF华安</t>
+          <t>港股通互联网ETF富国</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>sh518880</t>
+          <t>sz159792</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6.938</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
@@ -830,14 +830,14 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>8.92%</t>
+          <t>-3.21%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-05-08 13:04</t>
+          <t>2025-03-13 13:04</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -847,21 +847,21 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>黄金ETF华安</t>
+          <t>港股通互联网ETF富国</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>sh518880</t>
+          <t>sz159792</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>7.557</v>
+        <v>0.906</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>调出目标</t>
+          <t>盈利保护</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -869,7 +869,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-05-08 13:04</t>
+          <t>2025-03-13 13:04</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -879,16 +879,16 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>德国ETF华安</t>
+          <t>中概互联网ETF易方达</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>sh513030</t>
+          <t>sh513050</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1.848</v>
+        <v>1.476</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
@@ -898,14 +898,14 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>4.13%</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-05-14 13:04</t>
+          <t>2025-03-14 13:04</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -915,16 +915,16 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>德国ETF华安</t>
+          <t>中概互联网ETF易方达</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>sh513030</t>
+          <t>sh513050</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1.854</v>
+        <v>1.537</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
@@ -937,7 +937,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-05-14 13:04</t>
+          <t>2025-03-14 13:04</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -947,16 +947,16 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>东南亚科技ETF华泰柏瑞</t>
+          <t>港股通互联网ETF富国</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>sh513730</t>
+          <t>sz159792</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1.237</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
@@ -966,14 +966,14 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-2.18%</t>
+          <t>0.11%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-05-22 13:04</t>
+          <t>2025-03-17 13:04</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -983,16 +983,16 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>东南亚科技ETF华泰柏瑞</t>
+          <t>港股通互联网ETF富国</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>sh513730</t>
+          <t>sz159792</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1.21</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
@@ -1005,7 +1005,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-05-22 13:04</t>
+          <t>2025-03-17 13:04</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1015,16 +1015,16 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>纳指科技ETF景顺</t>
+          <t>港股红利ETF博时</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>sz159509</t>
+          <t>sh513690</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1.504</v>
+        <v>0.962</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
@@ -1034,14 +1034,14 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3.99%</t>
+          <t>-2.08%</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-06-11 13:04</t>
+          <t>2025-03-25 13:04</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1051,16 +1051,16 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>纳指科技ETF景顺</t>
+          <t>港股红利ETF博时</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>sz159509</t>
+          <t>sh513690</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1.564</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
@@ -1073,7 +1073,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-06-11 13:04</t>
+          <t>2025-03-25 13:04</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1083,16 +1083,16 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>白银LOF国投</t>
+          <t>有色ETF大成</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>sz161226</t>
+          <t>sz159980</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1.044</v>
+        <v>1.753</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
@@ -1102,14 +1102,14 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-1.82%</t>
+          <t>0.23%</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-06-19 13:04</t>
+          <t>2025-03-26 13:04</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1119,16 +1119,16 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>白银LOF国投</t>
+          <t>有色ETF大成</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>sz161226</t>
+          <t>sz159980</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1.025</v>
+        <v>1.757</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
@@ -1141,7 +1141,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025-06-19 13:04</t>
+          <t>2025-03-26 13:04</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1151,16 +1151,16 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>南方原油LOF</t>
+          <t>德国ETF华安</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>sh501018</t>
+          <t>sh513030</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1.441</v>
+        <v>1.795</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
@@ -1170,14 +1170,14 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-15.54%</t>
+          <t>-2.51%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2025-06-30 13:04</t>
+          <t>2025-03-28 13:04</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1187,16 +1187,16 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>南方原油LOF</t>
+          <t>德国ETF华安</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>sh501018</t>
+          <t>sh513030</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1.217</v>
+        <v>1.75</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
@@ -1209,7 +1209,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2025-06-30 13:04</t>
+          <t>2025-03-28 13:04</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1219,16 +1219,16 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>中韩半导体ETF华泰柏瑞</t>
+          <t>黄金ETF华安</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>sh513310</t>
+          <t>sh518880</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1.683</v>
+        <v>6.938</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
@@ -1238,14 +1238,14 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-3.33%</t>
+          <t>8.10%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2025-07-07 13:04</t>
+          <t>2025-04-23 13:04</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1255,21 +1255,21 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>中韩半导体ETF华泰柏瑞</t>
+          <t>黄金ETF华安</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>sh513310</t>
+          <t>sh518880</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1.627</v>
+        <v>7.5</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>调出目标</t>
+          <t>盈利保护</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
@@ -1277,7 +1277,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2025-07-07 13:04</t>
+          <t>2025-04-24 13:04</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1287,16 +1287,16 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>纳指科技ETF景顺</t>
+          <t>黄金ETF华安</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>sz159509</t>
+          <t>sh518880</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1.662</v>
+        <v>7.582</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
@@ -1306,14 +1306,14 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>5.78%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2025-07-25 13:04</t>
+          <t>2025-05-08 13:04</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1323,16 +1323,16 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>纳指科技ETF景顺</t>
+          <t>黄金ETF华安</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>sz159509</t>
+          <t>sh518880</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1.758</v>
+        <v>7.557</v>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
@@ -1345,7 +1345,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2025-07-25 13:04</t>
+          <t>2025-05-08 13:04</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1355,16 +1355,16 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>创业板ETF易方达</t>
+          <t>德国ETF华安</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>sz159915</t>
+          <t>sh513030</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2.318</v>
+        <v>1.848</v>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
@@ -1374,14 +1374,14 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>0.32%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2025-08-06 13:04</t>
+          <t>2025-05-14 13:04</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1391,16 +1391,16 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>创业板ETF易方达</t>
+          <t>德国ETF华安</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>sz159915</t>
+          <t>sh513030</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2.336</v>
+        <v>1.854</v>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
@@ -1413,7 +1413,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2025-08-06 13:04</t>
+          <t>2025-05-14 13:04</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1423,16 +1423,16 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>机器人ETF华夏</t>
+          <t>东南亚科技ETF华泰柏瑞</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>sh562500</t>
+          <t>sh513730</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.948</v>
+        <v>1.237</v>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
@@ -1442,14 +1442,14 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>5.17%</t>
+          <t>-2.18%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2025-08-20 13:04</t>
+          <t>2025-05-22 13:04</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1459,16 +1459,16 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>机器人ETF华夏</t>
+          <t>东南亚科技ETF华泰柏瑞</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>sh562500</t>
+          <t>sh513730</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.997</v>
+        <v>1.21</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
@@ -1481,7 +1481,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2025-08-20 13:04</t>
+          <t>2025-05-22 13:04</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1491,16 +1491,16 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>创业板成长ETF华夏</t>
+          <t>纳指科技ETF景顺</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>sz159967</t>
+          <t>sz159509</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.541</v>
+        <v>1.504</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
@@ -1510,14 +1510,14 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>3.51%</t>
+          <t>3.99%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2025-08-26 13:04</t>
+          <t>2025-06-11 13:04</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1527,16 +1527,16 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>创业板成长ETF华夏</t>
+          <t>纳指科技ETF景顺</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>sz159967</t>
+          <t>sz159509</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.564</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
@@ -1549,7 +1549,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2025-08-26 13:04</t>
+          <t>2025-06-11 13:04</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1559,16 +1559,16 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>科创50ETF易方达</t>
+          <t>白银LOF国投</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>sh588080</t>
+          <t>sz161226</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1.305</v>
+        <v>1.044</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
@@ -1578,14 +1578,14 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-0.61%</t>
+          <t>-1.82%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2025-09-08 13:04</t>
+          <t>2025-06-19 13:04</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1595,16 +1595,16 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>科创50ETF易方达</t>
+          <t>白银LOF国投</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>sh588080</t>
+          <t>sz161226</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1.297</v>
+        <v>1.025</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
@@ -1617,7 +1617,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2025-09-08 13:04</t>
+          <t>2025-06-19 13:04</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1627,16 +1627,16 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>创业板ETF易方达</t>
+          <t>南方原油LOF</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>sz159915</t>
+          <t>sh501018</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2.908</v>
+        <v>1.441</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
@@ -1646,14 +1646,14 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>5.30%</t>
+          <t>-7.01%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2025-09-19 13:04</t>
+          <t>2025-06-20 13:04</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1663,21 +1663,21 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>创业板ETF易方达</t>
+          <t>南方原油LOF</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>sz159915</t>
+          <t>sh501018</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3.062</v>
+        <v>1.34</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>调出目标</t>
+          <t>盈利保护</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
@@ -1685,7 +1685,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2025-09-19 13:04</t>
+          <t>2025-06-20 13:04</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1695,16 +1695,16 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>中韩半导体ETF华泰柏瑞</t>
+          <t>白银LOF国投</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>sh513310</t>
+          <t>sz161226</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2.165</v>
+        <v>1.004</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>8.55%</t>
+          <t>1.10%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2025-10-17 13:04</t>
+          <t>2025-06-23 13:04</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1731,16 +1731,16 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>中韩半导体ETF华泰柏瑞</t>
+          <t>白银LOF国投</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>sh513310</t>
+          <t>sz161226</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2.35</v>
+        <v>1.015</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
@@ -1753,7 +1753,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2025-10-17 13:04</t>
+          <t>2025-06-23 13:04</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1763,16 +1763,16 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>白银LOF国投</t>
+          <t>南方原油LOF</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>sz161226</t>
+          <t>sh501018</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1.469</v>
+        <v>1.439</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
@@ -1782,14 +1782,14 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-11.84%</t>
+          <t>-10.01%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2025-10-24 13:04</t>
+          <t>2025-06-24 13:04</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1799,12 +1799,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>白银LOF国投</t>
+          <t>南方原油LOF</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>sz161226</t>
+          <t>sh501018</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -1813,7 +1813,7 @@
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>调出目标</t>
+          <t>盈利保护</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
@@ -1821,7 +1821,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2025-10-24 13:04</t>
+          <t>2025-06-24 13:04</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1831,16 +1831,16 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>黄金ETF华安</t>
+          <t>中韩半导体ETF华泰柏瑞</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>sh518880</t>
+          <t>sh513310</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>8.949999999999999</v>
+        <v>1.644</v>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
@@ -1850,14 +1850,14 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-3.94%</t>
+          <t>1.76%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2025-10-28 13:04</t>
+          <t>2025-06-26 13:04</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1867,16 +1867,16 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>黄金ETF华安</t>
+          <t>中韩半导体ETF华泰柏瑞</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>sh518880</t>
+          <t>sh513310</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>8.597</v>
+        <v>1.673</v>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2025-10-28 13:04</t>
+          <t>2025-06-26 13:04</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1899,16 +1899,16 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>日经ETF华夏</t>
+          <t>南方原油LOF</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>sh513520</t>
+          <t>sh501018</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1.935</v>
+        <v>1.231</v>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
@@ -1918,14 +1918,14 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>-1.14%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2025-11-03 13:04</t>
+          <t>2025-06-30 13:04</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1935,16 +1935,16 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>日经ETF华夏</t>
+          <t>南方原油LOF</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>sh513520</t>
+          <t>sh501018</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1.993</v>
+        <v>1.217</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
@@ -1957,7 +1957,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2025-11-03 13:04</t>
+          <t>2025-06-30 13:04</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1976,7 +1976,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2.831</v>
+        <v>1.683</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
@@ -1986,14 +1986,14 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-9.78%</t>
+          <t>-3.33%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2025-11-14 13:04</t>
+          <t>2025-07-07 13:04</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2.554</v>
+        <v>1.627</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
@@ -2025,7 +2025,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2025-11-14 13:04</t>
+          <t>2025-07-07 13:04</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2035,16 +2035,16 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>纳指生物科技ETF汇添富</t>
+          <t>纳指科技ETF景顺</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>sh513290</t>
+          <t>sz159509</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1.475</v>
+        <v>1.662</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
@@ -2054,14 +2054,14 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>7.93%</t>
+          <t>5.78%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2025-12-01 13:04</t>
+          <t>2025-07-25 13:04</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2071,16 +2071,16 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>纳指生物科技ETF汇添富</t>
+          <t>纳指科技ETF景顺</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>sh513290</t>
+          <t>sz159509</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1.592</v>
+        <v>1.758</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
@@ -2093,7 +2093,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2025-12-01 13:04</t>
+          <t>2025-07-25 13:04</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2103,16 +2103,16 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>白银LOF国投</t>
+          <t>创业板ETF易方达</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>sz161226</t>
+          <t>sz159915</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1.617</v>
+        <v>2.318</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
@@ -2122,14 +2122,14 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>19.79%</t>
+          <t>0.78%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2025-12-11 13:04</t>
+          <t>2025-08-06 13:04</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2139,16 +2139,16 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>白银LOF国投</t>
+          <t>创业板ETF易方达</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>sz161226</t>
+          <t>sz159915</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1.937</v>
+        <v>2.336</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
@@ -2161,7 +2161,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2025-12-11 13:04</t>
+          <t>2025-08-06 13:04</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2171,16 +2171,16 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>纳指生物科技ETF汇添富</t>
+          <t>机器人ETF华夏</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>sh513290</t>
+          <t>sh562500</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1.593</v>
+        <v>0.948</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
@@ -2190,14 +2190,14 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-1.82%</t>
+          <t>5.17%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2025-12-15 13:04</t>
+          <t>2025-08-20 13:04</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2207,16 +2207,16 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>纳指生物科技ETF汇添富</t>
+          <t>机器人ETF华夏</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>sh513290</t>
+          <t>sh562500</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1.564</v>
+        <v>0.997</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
@@ -2229,7 +2229,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2025-12-15 13:04</t>
+          <t>2025-08-20 13:04</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2239,16 +2239,16 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>白银LOF国投</t>
+          <t>创业板成长ETF华夏</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>sz161226</t>
+          <t>sz159967</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2.016</v>
+        <v>0.541</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
@@ -2258,14 +2258,14 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>0.55%</t>
+          <t>3.51%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2025-12-16 13:04</t>
+          <t>2025-08-26 13:04</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2275,16 +2275,16 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>白银LOF国投</t>
+          <t>创业板成长ETF华夏</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>sz161226</t>
+          <t>sz159967</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2.027</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
@@ -2297,7 +2297,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2025-12-16 13:04</t>
+          <t>2025-08-26 13:04</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2307,16 +2307,16 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>创业板成长ETF华夏</t>
+          <t>科创50ETF易方达</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>sz159967</t>
+          <t>sh588080</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.607</v>
+        <v>1.305</v>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
@@ -2326,14 +2326,14 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>7.25%</t>
+          <t>-4.06%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2025-12-30 13:04</t>
+          <t>2025-09-04 13:04</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2343,21 +2343,21 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>创业板成长ETF华夏</t>
+          <t>科创50ETF易方达</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>sz159967</t>
+          <t>sh588080</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.651</v>
+        <v>1.252</v>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>调出目标</t>
+          <t>盈利保护</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
@@ -2365,7 +2365,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2025-12-30 13:04</t>
+          <t>2025-09-04 13:04</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2375,16 +2375,16 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>白银LOF国投</t>
+          <t>A500ETF华泰柏瑞</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>sz161226</t>
+          <t>sh563360</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2.377</v>
+        <v>1.158</v>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
@@ -2394,14 +2394,14 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>9.30%</t>
+          <t>2.59%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-01-06 13:04</t>
+          <t>2025-09-05 13:04</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2411,16 +2411,16 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>白银LOF国投</t>
+          <t>A500ETF华泰柏瑞</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>sz161226</t>
+          <t>sh563360</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2.598</v>
+        <v>1.188</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
@@ -2433,7 +2433,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-01-06 13:04</t>
+          <t>2025-09-05 13:04</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2443,16 +2443,16 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>有色ETF大成</t>
+          <t>科创50ETF易方达</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>sz159980</t>
+          <t>sh588080</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2.13</v>
+        <v>1.296</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
@@ -2462,14 +2462,14 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>0.08%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-01-07 13:04</t>
+          <t>2025-09-08 13:04</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2479,16 +2479,16 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>有色ETF大成</t>
+          <t>科创50ETF易方达</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>sz159980</t>
+          <t>sh588080</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2.126</v>
+        <v>1.297</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
@@ -2501,7 +2501,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-01-07 13:04</t>
+          <t>2025-09-08 13:04</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2511,16 +2511,16 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>中韩半导体ETF华泰柏瑞</t>
+          <t>创业板ETF易方达</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>sh513310</t>
+          <t>sz159915</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>3.126</v>
+        <v>2.908</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
@@ -2530,14 +2530,14 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>-3.68%</t>
+          <t>5.30%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-01-08 13:04</t>
+          <t>2025-09-19 13:04</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2547,16 +2547,16 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>中韩半导体ETF华泰柏瑞</t>
+          <t>创业板ETF易方达</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>sh513310</t>
+          <t>sz159915</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>3.011</v>
+        <v>3.062</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
@@ -2569,7 +2569,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-01-08 13:04</t>
+          <t>2025-09-19 13:04</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2579,16 +2579,16 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>白银LOF国投</t>
+          <t>中韩半导体ETF华泰柏瑞</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>sz161226</t>
+          <t>sh513310</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2.5</v>
+        <v>2.165</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
@@ -2598,14 +2598,14 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>8.40%</t>
+          <t>9.93%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-01-12 13:04</t>
+          <t>2025-10-10 13:04</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2615,21 +2615,21 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>白银LOF国投</t>
+          <t>中韩半导体ETF华泰柏瑞</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>sz161226</t>
+          <t>sh513310</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2.71</v>
+        <v>2.38</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>调出目标</t>
+          <t>盈利保护</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
@@ -2637,7 +2637,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-01-13 13:04</t>
+          <t>2025-10-10 13:04</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2647,16 +2647,16 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>中韩半导体ETF华泰柏瑞</t>
+          <t>白银LOF国投</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>sh513310</t>
+          <t>sz161226</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>3.001</v>
+        <v>1.286</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
@@ -2666,14 +2666,14 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>21.79%</t>
+          <t>5.75%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-02-03 13:04</t>
+          <t>2025-10-13 13:04</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2683,16 +2683,16 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>中韩半导体ETF华泰柏瑞</t>
+          <t>白银LOF国投</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>sh513310</t>
+          <t>sz161226</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>3.655</v>
+        <v>1.36</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
@@ -2705,7 +2705,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-02-03 13:04</t>
+          <t>2025-10-13 13:04</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2715,16 +2715,16 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>南方原油LOF</t>
+          <t>中韩半导体ETF华泰柏瑞</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>sh501018</t>
+          <t>sh513310</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1.257</v>
+        <v>2.402</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
@@ -2734,14 +2734,14 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>-3.25%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-02-04 13:04</t>
+          <t>2025-10-14 13:04</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2751,21 +2751,21 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>南方原油LOF</t>
+          <t>中韩半导体ETF华泰柏瑞</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>sh501018</t>
+          <t>sh513310</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1.242</v>
+        <v>2.324</v>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>调出目标</t>
+          <t>盈利保护</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
@@ -2773,7 +2773,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-02-05 13:04</t>
+          <t>2025-10-14 13:04</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2783,16 +2783,16 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>中韩半导体ETF华泰柏瑞</t>
+          <t>白银LOF国投</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>sh513310</t>
+          <t>sz161226</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3.415</v>
+        <v>1.356</v>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
@@ -2802,14 +2802,14 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>3.39%</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-02-11 13:04</t>
+          <t>2025-10-15 13:04</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2819,21 +2819,21 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>中韩半导体ETF华泰柏瑞</t>
+          <t>白银LOF国投</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>sh513310</t>
+          <t>sz161226</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3.422</v>
+        <v>1.402</v>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>调出目标</t>
+          <t>盈利保护</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
@@ -2841,7 +2841,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-02-11 13:04</t>
+          <t>2025-10-15 13:04</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2851,16 +2851,16 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>南方原油LOF</t>
+          <t>中韩半导体ETF华泰柏瑞</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>sh501018</t>
+          <t>sh513310</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1.348</v>
+        <v>2.382</v>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
@@ -2870,14 +2870,14 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>-2.30%</t>
+          <t>-1.34%</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-02-13 13:04</t>
+          <t>2025-10-17 13:04</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2887,16 +2887,16 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>南方原油LOF</t>
+          <t>中韩半导体ETF华泰柏瑞</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>sh501018</t>
+          <t>sh513310</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1.317</v>
+        <v>2.35</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
@@ -2909,7 +2909,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-02-13 13:04</t>
+          <t>2025-10-17 13:04</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2919,16 +2919,16 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>中韩半导体ETF华泰柏瑞</t>
+          <t>白银LOF国投</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>sh513310</t>
+          <t>sz161226</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3.603</v>
+        <v>1.469</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
@@ -2938,14 +2938,14 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>6.88%</t>
+          <t>-6.94%</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-02-24 13:04</t>
+          <t>2025-10-20 13:04</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2955,21 +2955,21 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>中韩半导体ETF华泰柏瑞</t>
+          <t>白银LOF国投</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>sh513310</t>
+          <t>sz161226</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>3.851</v>
+        <v>1.367</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>调出目标</t>
+          <t>盈利保护</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
@@ -2977,7 +2977,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-02-24 13:04</t>
+          <t>2025-10-20 13:04</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2987,16 +2987,16 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>日经ETF华夏</t>
+          <t>中韩半导体ETF华泰柏瑞</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>sh513520</t>
+          <t>sh513310</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2.105</v>
+        <v>2.385</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
@@ -3006,14 +3006,14 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>1.71%</t>
+          <t>0.88%</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-02-25 13:04</t>
+          <t>2025-10-21 13:04</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3023,16 +3023,16 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>日经ETF华夏</t>
+          <t>中韩半导体ETF华泰柏瑞</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>sh513520</t>
+          <t>sh513310</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2.141</v>
+        <v>2.406</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
@@ -3045,7 +3045,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-02-25 13:04</t>
+          <t>2025-10-21 13:04</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3055,16 +3055,16 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>中韩半导体ETF华泰柏瑞</t>
+          <t>白银LOF国投</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>sh513310</t>
+          <t>sz161226</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>3.941</v>
+        <v>1.356</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
@@ -3074,14 +3074,14 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>9.64%</t>
+          <t>-3.69%</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-02-26 13:04</t>
+          <t>2025-10-22 13:04</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3091,21 +3091,21 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>中韩半导体ETF华泰柏瑞</t>
+          <t>白银LOF国投</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>sh513310</t>
+          <t>sz161226</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4.321</v>
+        <v>1.306</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>调出目标</t>
+          <t>盈利保护</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
@@ -3113,7 +3113,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-02-26 13:04</t>
+          <t>2025-10-22 13:04</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3123,16 +3123,16 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>南方原油LOF</t>
+          <t>黄金ETF华安</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>sh501018</t>
+          <t>sh518880</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1.43</v>
+        <v>9.101000000000001</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
@@ -3142,14 +3142,14 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>-1.18%</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-02-27 13:04</t>
+          <t>2025-10-23 13:04</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3159,16 +3159,16 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>南方原油LOF</t>
+          <t>黄金ETF华安</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>sh501018</t>
+          <t>sh518880</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1.439</v>
+        <v>8.994</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
@@ -3181,7 +3181,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-02-27 13:04</t>
+          <t>2025-10-23 13:04</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3191,16 +3191,16 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>中韩半导体ETF华泰柏瑞</t>
+          <t>白银LOF国投</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>sh513310</t>
+          <t>sz161226</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4.256</v>
+        <v>1.31</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
@@ -3210,14 +3210,14 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>-3.69%</t>
+          <t>-1.15%</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-03-05 13:04</t>
+          <t>2025-10-24 13:04</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3227,16 +3227,16 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>中韩半导体ETF华泰柏瑞</t>
+          <t>白银LOF国投</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>sh513310</t>
+          <t>sz161226</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4.099</v>
+        <v>1.295</v>
       </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
@@ -3249,7 +3249,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-03-06 13:04</t>
+          <t>2025-10-24 13:04</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3259,16 +3259,16 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>南方原油LOF</t>
+          <t>黄金ETF华安</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>sh501018</t>
+          <t>sh518880</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1.579</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
@@ -3278,14 +3278,14 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>40.15%</t>
+          <t>-3.94%</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-03-19 13:04</t>
+          <t>2025-10-28 13:04</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3295,16 +3295,16 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>南方原油LOF</t>
+          <t>黄金ETF华安</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>sh501018</t>
+          <t>sh518880</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2.213</v>
+        <v>8.597</v>
       </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
@@ -3317,7 +3317,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-03-20 13:04</t>
+          <t>2025-10-28 13:04</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3327,16 +3327,16 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>能源化工ETF建信</t>
+          <t>日经ETF华夏</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>sz159981</t>
+          <t>sh513520</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1.662</v>
+        <v>1.935</v>
       </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
@@ -3346,14 +3346,14 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>-3.31%</t>
+          <t>3.00%</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-04-01 13:04</t>
+          <t>2025-11-03 13:04</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3363,16 +3363,16 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>能源化工ETF建信</t>
+          <t>日经ETF华夏</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>sz159981</t>
+          <t>sh513520</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1.607</v>
+        <v>1.993</v>
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
@@ -3385,7 +3385,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-04-01 13:04</t>
+          <t>2025-11-03 13:04</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3395,16 +3395,16 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>南方原油LOF</t>
+          <t>中韩半导体ETF华泰柏瑞</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>sh501018</t>
+          <t>sh513310</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2.087</v>
+        <v>2.831</v>
       </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
@@ -3414,14 +3414,14 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>8.91%</t>
+          <t>-5.19%</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-04-02 13:04</t>
+          <t>2025-11-04 13:04</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3431,21 +3431,21 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>南方原油LOF</t>
+          <t>中韩半导体ETF华泰柏瑞</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>sh501018</t>
+          <t>sh513310</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2.273</v>
+        <v>2.684</v>
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>调出目标</t>
+          <t>盈利保护</t>
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
@@ -3453,7 +3453,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-04-02 13:04</t>
+          <t>2025-11-04 13:04</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3463,16 +3463,16 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>能源化工ETF建信</t>
+          <t>日经ETF华夏</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>sz159981</t>
+          <t>sh513520</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1.699</v>
+        <v>1.93</v>
       </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
@@ -3482,14 +3482,14 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>-4.36%</t>
+          <t>-0.93%</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-04-13 13:04</t>
+          <t>2025-11-05 13:04</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3499,21 +3499,21 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>能源化工ETF建信</t>
+          <t>日经ETF华夏</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>sz159981</t>
+          <t>sh513520</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1.625</v>
+        <v>1.912</v>
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>调出目标</t>
+          <t>盈利保护</t>
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
@@ -3521,7 +3521,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-04-13 13:04</t>
+          <t>2025-11-05 13:04</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3531,16 +3531,16 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>创业板成长ETF华夏</t>
+          <t>纳指生物科技ETF汇添富</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>sz159967</t>
+          <t>sh513290</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.717</v>
+        <v>1.415</v>
       </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
@@ -3550,14 +3550,14 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>14.64%</t>
+          <t>1.41%</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-05-07 13:04</t>
+          <t>2025-11-06 13:04</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3567,16 +3567,16 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>创业板成长ETF华夏</t>
+          <t>纳指生物科技ETF汇添富</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>sz159967</t>
+          <t>sh513290</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.822</v>
+        <v>1.435</v>
       </c>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
@@ -3589,7 +3589,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-05-07 13:04</t>
+          <t>2025-11-06 13:04</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3608,7 +3608,7 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5.057</v>
+        <v>2.689</v>
       </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
@@ -3618,14 +3618,14 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>11.41%</t>
+          <t>-5.02%</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-05-11 13:04</t>
+          <t>2025-11-14 13:04</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3644,12 +3644,12 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5.634</v>
+        <v>2.554</v>
       </c>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>调出目标</t>
+          <t>盈利保护</t>
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
@@ -3657,7 +3657,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-05-11 13:04</t>
+          <t>2025-11-14 13:04</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3667,16 +3667,16 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>科创50ETF易方达</t>
+          <t>纳指生物科技ETF汇添富</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>sh588080</t>
+          <t>sh513290</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1.754</v>
+        <v>1.475</v>
       </c>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
@@ -3686,14 +3686,14 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.88%</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-05-12 13:04</t>
+          <t>2025-11-20 13:04</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3703,21 +3703,21 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>科创50ETF易方达</t>
+          <t>纳指生物科技ETF汇添富</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>sh588080</t>
+          <t>sh513290</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1.761</v>
+        <v>1.488</v>
       </c>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>调出目标</t>
+          <t>盈利保护</t>
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
@@ -3725,7 +3725,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-05-12 13:04</t>
+          <t>2025-11-20 13:04</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3735,16 +3735,16 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>中韩半导体ETF华泰柏瑞</t>
+          <t>港股红利ETF博时</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>sh513310</t>
+          <t>sh513690</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5.598</v>
+        <v>1.137</v>
       </c>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
@@ -3754,14 +3754,14 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>9.57%</t>
+          <t>-1.23%</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-05-13 13:04</t>
+          <t>2025-11-21 13:04</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3771,16 +3771,16 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>中韩半导体ETF华泰柏瑞</t>
+          <t>港股红利ETF博时</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>sh513310</t>
+          <t>sh513690</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6.134</v>
+        <v>1.123</v>
       </c>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
@@ -3793,7 +3793,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-05-13 13:04</t>
+          <t>2025-11-21 13:04</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3803,16 +3803,16 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>科创50ETF易方达</t>
+          <t>纳指生物科技ETF汇添富</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>sh588080</t>
+          <t>sh513290</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1.808</v>
+        <v>1.457</v>
       </c>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
@@ -3822,14 +3822,14 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>9.27%</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-05-19 13:04</t>
+          <t>2025-12-01 13:04</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3839,16 +3839,16 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>科创50ETF易方达</t>
+          <t>纳指生物科技ETF汇添富</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>sh588080</t>
+          <t>sh513290</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1.815</v>
+        <v>1.592</v>
       </c>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
@@ -3861,7 +3861,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-05-19 13:04</t>
+          <t>2025-12-01 13:04</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3871,16 +3871,16 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>中韩半导体ETF华泰柏瑞</t>
+          <t>白银LOF国投</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>sh513310</t>
+          <t>sz161226</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5.323</v>
+        <v>1.617</v>
       </c>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
@@ -3890,14 +3890,14 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>25.36%</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-05-20 13:04</t>
+          <t>2025-12-16 13:04</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3907,16 +3907,16 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>中韩半导体ETF华泰柏瑞</t>
+          <t>白银LOF国投</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>sh513310</t>
+          <t>sz161226</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5.382</v>
+        <v>2.027</v>
       </c>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
@@ -3929,7 +3929,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-05-20 13:04</t>
+          <t>2025-12-16 13:04</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3939,16 +3939,16 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>科创50ETF易方达</t>
+          <t>创业板成长ETF华夏</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>sh588080</t>
+          <t>sz159967</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1.87</v>
+        <v>0.607</v>
       </c>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
@@ -3958,14 +3958,14 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>-2.14%</t>
+          <t>6.43%</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-05-22 13:04</t>
+          <t>2025-12-29 13:04</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3975,16 +3975,16 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>科创50ETF易方达</t>
+          <t>创业板成长ETF华夏</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>sh588080</t>
+          <t>sz159967</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1.83</v>
+        <v>0.646</v>
       </c>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
@@ -3997,7 +3997,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-05-22 13:04</t>
+          <t>2025-12-29 13:04</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4007,16 +4007,16 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>中韩半导体ETF华泰柏瑞</t>
+          <t>白银LOF国投</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>sh513310</t>
+          <t>sz161226</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>5.708</v>
+        <v>2.543</v>
       </c>
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
@@ -4026,14 +4026,14 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>5.83%</t>
+          <t>-6.53%</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-05-25 13:04</t>
+          <t>2025-12-30 13:04</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4043,21 +4043,21 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>中韩半导体ETF华泰柏瑞</t>
+          <t>白银LOF国投</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>sh513310</t>
+          <t>sz161226</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6.041</v>
+        <v>2.377</v>
       </c>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>调出目标</t>
+          <t>盈利保护</t>
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
@@ -4065,7 +4065,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-05-25 13:04</t>
+          <t>2025-12-30 13:04</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4075,16 +4075,16 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>科创50ETF易方达</t>
+          <t>创业板成长ETF华夏</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>sh588080</t>
+          <t>sz159967</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1.936</v>
+        <v>0.651</v>
       </c>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
@@ -4092,12 +4092,16 @@
           <t>排名1</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr"/>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>-2.30%</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-06-03 01:07</t>
+          <t>2025-12-31 13:04</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4107,23 +4111,21 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>科创50ETF易方达</t>
+          <t>创业板成长ETF华夏</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>sh588080</t>
+          <t>sz159967</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1.727</v>
-      </c>
-      <c r="F109" t="n">
-        <v>8.638500000000001</v>
-      </c>
+        <v>0.636</v>
+      </c>
+      <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>排名从2→新第1不等,调出</t>
+          <t>调出目标</t>
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
@@ -4131,7 +4133,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-06-03 01:07</t>
+          <t>2025-12-31 13:04</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4141,26 +4143,2812 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
+          <t>有色ETF大成</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>sz159980</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>1.996</v>
+      </c>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>排名1</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>2.96%</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-01-05 13:04</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>有色ETF大成</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>sz159980</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>2.055</v>
+      </c>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>调出目标</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-01-05 13:04</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>白银LOF国投</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>sz161226</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>2.372</v>
+      </c>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>排名1</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>9.53%</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-01-06 13:04</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>白银LOF国投</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>sz161226</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>2.598</v>
+      </c>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>调出目标</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-01-06 13:04</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>有色ETF大成</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>sz159980</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>排名1</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>-0.19%</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-01-07 13:04</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>有色ETF大成</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>sz159980</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>2.126</v>
+      </c>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>调出目标</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-01-07 13:04</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>白银LOF国投</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>sz161226</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>2.565</v>
+      </c>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>排名1</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>-2.53%</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-01-08 13:04</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>白银LOF国投</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>sz161226</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>盈利保护</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-01-08 13:04</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>有色ETF大成</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>sz159980</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>2.073</v>
+      </c>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>排名1</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>0.63%</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-01-09 13:04</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>有色ETF大成</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>sz159980</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>2.086</v>
+      </c>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>调出目标</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-01-09 13:04</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>中证500ETF南方</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>sh510500</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>8.215999999999999</v>
+      </c>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>排名1</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>2.43%</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-01-12 13:04</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>中证500ETF南方</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>sh510500</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>8.416</v>
+      </c>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>调出目标</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-01-12 13:04</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
           <t>中韩半导体ETF华泰柏瑞</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr">
+      <c r="D122" t="inlineStr">
         <is>
           <t>sh513310</t>
         </is>
       </c>
-      <c r="E110" t="n">
+      <c r="E122" t="n">
+        <v>3.068</v>
+      </c>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>排名1</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>-2.18%</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-01-13 13:04</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>中韩半导体ETF华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>sh513310</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>3.001</v>
+      </c>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>调出目标</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-01-13 13:04</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>白银LOF国投</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>sz161226</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>2.748</v>
+      </c>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>排名1</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>12.59%</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-01-16 13:04</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>白银LOF国投</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>sz161226</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>3.094</v>
+      </c>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>调出目标</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-01-16 13:04</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>中韩半导体ETF华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>sh513310</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>3.159</v>
+      </c>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>排名1</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>6.52%</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-02-02 13:04</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>中韩半导体ETF华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>sh513310</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>3.365</v>
+      </c>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>盈利保护</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-02-02 13:04</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>科创50ETF易方达</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>sh588080</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>1.481</v>
+      </c>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>排名1</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>1.22%</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-02-03 13:04</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>科创50ETF易方达</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>sh588080</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>1.499</v>
+      </c>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>调出目标</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-02-03 13:04</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>中韩半导体ETF华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>sh513310</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>3.655</v>
+      </c>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>排名1</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>-6.57%</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-02-05 13:04</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>中韩半导体ETF华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>sh513310</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>3.415</v>
+      </c>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>盈利保护</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-02-05 13:04</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>黄金ETF华安</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>sh518880</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>10.523</v>
+      </c>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>排名1</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>-1.58%</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-02-06 13:04</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>黄金ETF华安</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>sh518880</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>10.357</v>
+      </c>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>调出目标</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-02-06 13:04</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>中韩半导体ETF华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>sh513310</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>3.405</v>
+      </c>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>排名1</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>0.50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-02-11 13:04</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>中韩半导体ETF华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>sh513310</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>3.422</v>
+      </c>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>调出目标</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-02-11 13:04</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>南方原油LOF</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>sh501018</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>1.348</v>
+      </c>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>排名1</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>0.82%</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-02-12 13:04</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>南方原油LOF</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>sh501018</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>1.359</v>
+      </c>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>盈利保护</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-02-12 13:04</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>中韩半导体ETF华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>sh513310</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>3.539</v>
+      </c>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>排名1</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>22.10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-02-26 13:04</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>中韩半导体ETF华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>sh513310</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>4.321</v>
+      </c>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>调出目标</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-02-26 13:04</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>日经ETF华夏</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>sh513520</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>2.123</v>
+      </c>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>排名1</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>0.24%</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-02-27 13:04</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>日经ETF华夏</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>sh513520</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>2.128</v>
+      </c>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>调出目标</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-02-27 13:04</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>南方原油LOF</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>sh501018</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>1.439</v>
+      </c>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>排名1</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>20.99%</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-03-03 13:04</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>南方原油LOF</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>sh501018</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>1.741</v>
+      </c>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>调出目标</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-03-03 13:04</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>港股红利ETF博时</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>sh513690</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>1.191</v>
+      </c>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>排名1</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>-0.92%</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:04</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>港股红利ETF博时</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>sh513690</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>调出目标</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:04</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>日经ETF华夏</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>sh513520</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>1.973</v>
+      </c>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>排名1</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>0.51%</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-03-06 13:04</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>日经ETF华夏</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>sh513520</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>1.983</v>
+      </c>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>调出目标</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-03-06 13:04</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>豆粕ETF华夏</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>sz159985</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>2.126</v>
+      </c>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>排名1</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>4.99%</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-03-09 13:04</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>豆粕ETF华夏</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>sz159985</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>2.232</v>
+      </c>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>调出目标</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-03-09 13:04</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>南方原油LOF</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>sh501018</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>1.737</v>
+      </c>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>排名1</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>27.40%</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-03-19 13:04</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>南方原油LOF</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>sh501018</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>2.213</v>
+      </c>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>调出目标</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-03-19 13:04</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>能源化工ETF建信</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>sz159981</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>1.701</v>
+      </c>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>排名1</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>-2.59%</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-03-25 13:04</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>能源化工ETF建信</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>sz159981</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>1.657</v>
+      </c>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>盈利保护</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-03-25 13:04</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>创业板成长ETF华夏</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>sz159967</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>排名1</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>-1.22%</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-03-26 13:04</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>创业板成长ETF华夏</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>sz159967</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>0.648</v>
+      </c>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>调出目标</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-03-26 13:04</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>能源化工ETF建信</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>sz159981</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>排名1</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>0.58%</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-03-31 13:04</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>能源化工ETF建信</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>sz159981</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>盈利保护</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-03-31 13:04</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>创业板成长ETF华夏</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>sz159967</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>0.624</v>
+      </c>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>排名1</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-04-02 13:04</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>创业板成长ETF华夏</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>sz159967</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>0.624</v>
+      </c>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>调出目标</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-04-02 13:04</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>能源化工ETF建信</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>sz159981</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>1.699</v>
+      </c>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>排名1</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>-3.47%</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-04-08 13:04</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>能源化工ETF建信</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>sz159981</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>盈利保护</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-04-08 13:04</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>创业板成长ETF华夏</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>sz159967</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>0.6820000000000001</v>
+      </c>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>排名1</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-04-09 13:04</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>创业板成长ETF华夏</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>sz159967</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>0.6820000000000001</v>
+      </c>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>调出目标</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-04-09 13:04</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>能源化工ETF建信</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>sz159981</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>1.663</v>
+      </c>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>排名1</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>-2.29%</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-04-13 13:04</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>能源化工ETF建信</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>sz159981</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>调出目标</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-04-13 13:04</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>创业板成长ETF华夏</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>sz159967</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>0.717</v>
+      </c>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>排名1</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>8.37%</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-04-24 13:04</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>创业板成长ETF华夏</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>sz159967</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>0.777</v>
+      </c>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>盈利保护</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-04-24 13:04</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>纳指科技ETF景顺</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>sz159509</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>2.296</v>
+      </c>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>排名1</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>3.22%</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-04-27 13:04</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>纳指科技ETF景顺</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>sz159509</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>调出目标</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-04-27 13:04</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>创业板成长ETF华夏</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>sz159967</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>0.776</v>
+      </c>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>排名1</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>2.84%</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-05-06 13:04</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>创业板成长ETF华夏</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>sz159967</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>0.798</v>
+      </c>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>调出目标</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-05-06 13:04</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>纳指科技ETF景顺</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>sz159509</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>2.542</v>
+      </c>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>排名1</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>0.12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-05-07 13:04</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>纳指科技ETF景顺</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>sz159509</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>2.545</v>
+      </c>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>调出目标</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-05-07 13:04</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>中韩半导体ETF华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>sh513310</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>5.057</v>
+      </c>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>排名1</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>10.70%</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-05-12 13:04</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>中韩半导体ETF华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>sh513310</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>5.598</v>
+      </c>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>调出目标</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-05-12 13:04</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>科创50ETF易方达</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>sh588080</t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>1.761</v>
+      </c>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>排名1</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>-1.59%</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:04</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>科创50ETF易方达</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>sh588080</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>1.733</v>
+      </c>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>盈利保护</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:04</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>纳指科技ETF景顺</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>sz159509</t>
+        </is>
+      </c>
+      <c r="E178" t="n">
+        <v>2.554</v>
+      </c>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>排名1</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>-2.82%</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-05-18 13:04</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>纳指科技ETF景顺</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>sz159509</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>2.482</v>
+      </c>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>调出目标</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-05-18 13:04</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>科创50ETF易方达</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>sh588080</t>
+        </is>
+      </c>
+      <c r="E180" t="n">
+        <v>1.747</v>
+      </c>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>排名1</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>7.04%</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:04</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>科创50ETF易方达</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>sh588080</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>调出目标</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:04</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>中韩半导体ETF华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>sh513310</t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>5.382</v>
+      </c>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>排名1</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>12.24%</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-05-25 13:04</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>中韩半导体ETF华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>sh513310</t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>6.041</v>
+      </c>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>调出目标</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-05-25 13:04</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>科创50ETF易方达</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>sh588080</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>1.936</v>
+      </c>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>排名1</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>-7.49%</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-05-29 13:04</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>科创50ETF易方达</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>sh588080</t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>1.791</v>
+      </c>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>盈利保护</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-05-29 13:04</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>创业板成长ETF华夏</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>sz159967</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>0.931</v>
+      </c>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>排名1</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>-3.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:04</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>创业板成长ETF华夏</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>sz159967</t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>0.894</v>
+      </c>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>盈利保护</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:04</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>纳指ETF国泰</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>sh513100</t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>排名1</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>-0.93%</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-06-02 13:04</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>纳指ETF国泰</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>sh513100</t>
+        </is>
+      </c>
+      <c r="E189" t="n">
+        <v>2.343</v>
+      </c>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>调出目标</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-06-02 13:04</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>中韩半导体ETF华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>sh513310</t>
+        </is>
+      </c>
+      <c r="E190" t="n">
         <v>5.942</v>
       </c>
-      <c r="F110" t="n">
-        <v>105.0035</v>
-      </c>
-      <c r="G110" t="inlineStr">
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>排名1</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:58</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>中韩半导体ETF华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>sh513310</t>
+        </is>
+      </c>
+      <c r="E191" t="n">
+        <v>6.117</v>
+      </c>
+      <c r="F191" t="n">
+        <v>16.1601</v>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>被过滤规则拦截调出: 溢价&gt;22%</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:58</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>创业板成长ETF华夏</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>sz159967</t>
+        </is>
+      </c>
+      <c r="E192" t="n">
+        <v>0.987</v>
+      </c>
+      <c r="F192" t="n">
+        <v>5.8452</v>
+      </c>
+      <c r="G192" t="inlineStr">
         <is>
           <t>动量排名第1/40</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr"/>
+      <c r="H192" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backtest/results_172/七星172_交易记录_2026.xlsx
+++ b/backtest/results_172/七星172_交易记录_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H192"/>
+  <dimension ref="A1:H194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6950,6 +6950,74 @@
       </c>
       <c r="H192" t="inlineStr"/>
     </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-06-04 13:05</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>创业板成长ETF华夏</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>sz159967</t>
+        </is>
+      </c>
+      <c r="E193" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="F193" t="n">
+        <v>5.2731</v>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>排名从1→新第1不等,调出</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-06-04 13:05</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>中韩半导体ETF华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>sh513310</t>
+        </is>
+      </c>
+      <c r="E194" t="n">
+        <v>6.017</v>
+      </c>
+      <c r="F194" t="n">
+        <v>15.0724</v>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>动量排名第1/40</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backtest/results_172/七星172_交易记录_2026.xlsx
+++ b/backtest/results_172/七星172_交易记录_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H194"/>
+  <dimension ref="A1:H208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7018,6 +7018,482 @@
       </c>
       <c r="H194" t="inlineStr"/>
     </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-06-05 13:01</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>中韩半导体ETF华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>sh513310</t>
+        </is>
+      </c>
+      <c r="E195" t="n">
+        <v>5.712</v>
+      </c>
+      <c r="F195" t="n">
+        <v>11.9173</v>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>被过滤规则拦截调出: 盈利保护</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-06-05 13:01</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>创业板成长ETF华夏</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>sz159967</t>
+        </is>
+      </c>
+      <c r="E196" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F196" t="n">
+        <v>5.0505</v>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>动量排名第1/40</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-06-08 13:22</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>创业板成长ETF华夏</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>sz159967</t>
+        </is>
+      </c>
+      <c r="E197" t="n">
+        <v>0.888</v>
+      </c>
+      <c r="F197" t="n">
+        <v>3.5728</v>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>被过滤规则拦截调出: 盈利保护</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-06-08 13:22</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>日经ETF华夏</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>sh513520</t>
+        </is>
+      </c>
+      <c r="E198" t="n">
+        <v>2.226</v>
+      </c>
+      <c r="F198" t="n">
+        <v>1.1679</v>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>动量排名第1/40</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-06-09 10:58</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>日经ETF华夏</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>sh513520</t>
+        </is>
+      </c>
+      <c r="E199" t="n">
+        <v>2.309</v>
+      </c>
+      <c r="F199" t="n">
+        <v>1.4665</v>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>排名从2→新第1不等,调出</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-06-09 10:58</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>创业板成长ETF华夏</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>sz159967</t>
+        </is>
+      </c>
+      <c r="E200" t="n">
+        <v>0.902</v>
+      </c>
+      <c r="F200" t="n">
+        <v>3.916</v>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>动量排名第1/40</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-06-11 13:04</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>创业板成长ETF华夏</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>sz159967</t>
+        </is>
+      </c>
+      <c r="E201" t="n">
+        <v>0.892</v>
+      </c>
+      <c r="F201" t="n">
+        <v>3.671</v>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>被过滤规则拦截调出: 盈利保护</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-06-11 13:04</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>日经ETF华夏</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>sh513520</t>
+        </is>
+      </c>
+      <c r="E202" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="F202" t="n">
+        <v>1.1833</v>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>动量排名第1/40</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-06-12 10:59</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>日经ETF华夏</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>sh513520</t>
+        </is>
+      </c>
+      <c r="E203" t="n">
+        <v>2.326</v>
+      </c>
+      <c r="F203" t="n">
+        <v>1.5214</v>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>排名从2→新第1不等,调出</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-06-12 10:59</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>中韩半导体ETF华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>sh513310</t>
+        </is>
+      </c>
+      <c r="E204" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="F204" t="n">
+        <v>14.3603</v>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>动量排名第1/40</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-06-12 13:02</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>中韩半导体ETF华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>sh513310</t>
+        </is>
+      </c>
+      <c r="E205" t="n">
+        <v>5.966</v>
+      </c>
+      <c r="F205" t="n">
+        <v>14.5291</v>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>被过滤规则拦截调出: 溢价&gt;25%</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-06-12 13:02</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>创业板成长ETF华夏</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>sz159967</t>
+        </is>
+      </c>
+      <c r="E206" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="F206" t="n">
+        <v>4.038</v>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>动量排名第1/40</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:58</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>创业板成长ETF华夏</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>sz159967</t>
+        </is>
+      </c>
+      <c r="E207" t="n">
+        <v>0.976</v>
+      </c>
+      <c r="F207" t="n">
+        <v>5.6173</v>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>排名从2→新第1不等,调出</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:58</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>中韩半导体ETF华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>sh513310</t>
+        </is>
+      </c>
+      <c r="E208" t="n">
+        <v>6.002</v>
+      </c>
+      <c r="F208" t="n">
+        <v>14.9118</v>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>动量排名第1/40</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backtest/results_172/七星172_交易记录_2026.xlsx
+++ b/backtest/results_172/七星172_交易记录_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H208"/>
+  <dimension ref="A1:H210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7494,6 +7494,74 @@
       </c>
       <c r="H208" t="inlineStr"/>
     </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-06-25 10:57</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>中韩半导体ETF华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>sh513310</t>
+        </is>
+      </c>
+      <c r="E209" t="n">
+        <v>6.513</v>
+      </c>
+      <c r="F209" t="n">
+        <v>0.2797</v>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>排名从5→新第1不等,调出</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-06-25 10:57</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>日经ETF华夏</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>sh513520</t>
+        </is>
+      </c>
+      <c r="E210" t="n">
+        <v>2.542</v>
+      </c>
+      <c r="F210" t="n">
+        <v>4.0462</v>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>动量排名第1/38</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backtest/results_172/七星172_交易记录_2026.xlsx
+++ b/backtest/results_172/七星172_交易记录_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H210"/>
+  <dimension ref="A1:H236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7562,6 +7562,890 @@
       </c>
       <c r="H210" t="inlineStr"/>
     </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-07-09 10:57</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>日经ETF华夏</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>sh513520</t>
+        </is>
+      </c>
+      <c r="E211" t="n">
+        <v>2.347</v>
+      </c>
+      <c r="F211" t="n">
+        <v>2.5904</v>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>被过滤规则拦截调出: 盈利保护</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-07-09 10:57</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>科创50ETF易方达</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>sh588080</t>
+        </is>
+      </c>
+      <c r="E212" t="n">
+        <v>2.132</v>
+      </c>
+      <c r="F212" t="n">
+        <v>0.3913</v>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>动量排名第1/38</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-07-13 10:57</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>科创50ETF易方达</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>sh588080</t>
+        </is>
+      </c>
+      <c r="E213" t="n">
+        <v>2.108</v>
+      </c>
+      <c r="F213" t="n">
+        <v>5.4817</v>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>被过滤规则拦截调出: 盈利保护</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-07-13 10:57</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>豆粕ETF华夏</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>sz159985</t>
+        </is>
+      </c>
+      <c r="E214" t="n">
+        <v>2.195</v>
+      </c>
+      <c r="F214" t="n">
+        <v>1.3377</v>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>动量排名第1/38</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-07-14 10:56</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>豆粕ETF华夏</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>sz159985</t>
+        </is>
+      </c>
+      <c r="E215" t="n">
+        <v>2.196</v>
+      </c>
+      <c r="F215" t="n">
+        <v>1.3406</v>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>排名从3→新第1不等,调出</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-07-14 10:56</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>纳指生物科技ETF汇添富</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>sh513290</t>
+        </is>
+      </c>
+      <c r="E216" t="n">
+        <v>1.601</v>
+      </c>
+      <c r="F216" t="n">
+        <v>5.6824</v>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>动量排名第1/38</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-07-20 13:15</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>纳指生物科技ETF汇添富</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>sh513290</t>
+        </is>
+      </c>
+      <c r="E217" t="n">
+        <v>1.601</v>
+      </c>
+      <c r="F217" t="n">
+        <v>0.6417</v>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>排名从1→新第1不等,调出</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-07-20 13:15</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>豆粕ETF华夏</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>sz159985</t>
+        </is>
+      </c>
+      <c r="E218" t="n">
+        <v>2.161</v>
+      </c>
+      <c r="F218" t="n">
+        <v>1.7288</v>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>动量排名第1/38</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-07-21 10:58</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>豆粕ETF华夏</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>sz159985</t>
+        </is>
+      </c>
+      <c r="E219" t="n">
+        <v>2.177</v>
+      </c>
+      <c r="F219" t="n">
+        <v>1.5193</v>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>排名从2→新第1不等,调出</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-07-21 10:58</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>南方原油LOF</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>sh501018</t>
+        </is>
+      </c>
+      <c r="E220" t="n">
+        <v>1.992</v>
+      </c>
+      <c r="F220" t="n">
+        <v>1.7343</v>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>动量排名第1/38</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-07-22 10:57</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>南方原油LOF</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>sh501018</t>
+        </is>
+      </c>
+      <c r="E221" t="n">
+        <v>2.098</v>
+      </c>
+      <c r="F221" t="n">
+        <v>6.623</v>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>被过滤规则拦截调出: 溢价&gt;22%</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-07-22 10:57</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>中概互联网ETF易方达</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>sh513050</t>
+        </is>
+      </c>
+      <c r="E222" t="n">
+        <v>1.097</v>
+      </c>
+      <c r="F222" t="n">
+        <v>2.2989</v>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>动量排名第1/38</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-07-22 13:00</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>中概互联网ETF易方达</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>sh513050</t>
+        </is>
+      </c>
+      <c r="E223" t="n">
+        <v>1.093</v>
+      </c>
+      <c r="F223" t="n">
+        <v>2.2465</v>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>被过滤规则拦截调出: 盈利保护</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-07-22 13:00</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>豆粕ETF华夏</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>sz159985</t>
+        </is>
+      </c>
+      <c r="E224" t="n">
+        <v>2.208</v>
+      </c>
+      <c r="F224" t="n">
+        <v>1.7925</v>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>动量排名第1/38</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-07-23 10:56</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>豆粕ETF华夏</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>sz159985</t>
+        </is>
+      </c>
+      <c r="E225" t="n">
+        <v>2.249</v>
+      </c>
+      <c r="F225" t="n">
+        <v>2.0447</v>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>排名从2→新第1不等,调出</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-07-23 10:56</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>中概互联网ETF易方达</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>sh513050</t>
+        </is>
+      </c>
+      <c r="E226" t="n">
+        <v>1.095</v>
+      </c>
+      <c r="F226" t="n">
+        <v>2.3124</v>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>动量排名第1/38</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-07-24 10:57</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>中概互联网ETF易方达</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>sh513050</t>
+        </is>
+      </c>
+      <c r="E227" t="n">
+        <v>1.065</v>
+      </c>
+      <c r="F227" t="n">
+        <v>1.5969</v>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>排名从2→新第1不等,调出</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-07-24 10:57</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>豆粕ETF华夏</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>sz159985</t>
+        </is>
+      </c>
+      <c r="E228" t="n">
+        <v>2.259</v>
+      </c>
+      <c r="F228" t="n">
+        <v>2.224</v>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>动量排名第1/38</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-07-28 20:33</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>豆粕ETF华夏</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>sz159985</t>
+        </is>
+      </c>
+      <c r="E229" t="n">
+        <v>2.121</v>
+      </c>
+      <c r="F229" t="n">
+        <v>1.365</v>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>被过滤规则拦截调出: 盈利保护</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-07-28 20:33</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>港股红利ETF博时</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>sh513690</t>
+        </is>
+      </c>
+      <c r="E230" t="n">
+        <v>1.145</v>
+      </c>
+      <c r="F230" t="n">
+        <v>2.1186</v>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>动量排名第1/38</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-07-29 10:57</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>港股红利ETF博时</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>sh513690</t>
+        </is>
+      </c>
+      <c r="E231" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="F231" t="n">
+        <v>2.5103</v>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>排名从2→新第1不等,调出</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-07-29 10:57</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>南方原油LOF</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>sh501018</t>
+        </is>
+      </c>
+      <c r="E232" t="n">
+        <v>1.909</v>
+      </c>
+      <c r="F232" t="n">
+        <v>20.3812</v>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>动量排名第1/38</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-08-05 10:57</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>南方原油LOF</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>sh501018</t>
+        </is>
+      </c>
+      <c r="E233" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F233" t="n">
+        <v>2.923</v>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>被过滤规则拦截调出: 盈利保护</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-08-05 10:57</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>恒生ETF华夏</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>sz159920</t>
+        </is>
+      </c>
+      <c r="E234" t="n">
+        <v>1.526</v>
+      </c>
+      <c r="F234" t="n">
+        <v>1.7977</v>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>动量排名第1/38</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-08-06 10:57</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>恒生ETF华夏</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>sz159920</t>
+        </is>
+      </c>
+      <c r="E235" t="n">
+        <v>1.502</v>
+      </c>
+      <c r="F235" t="n">
+        <v>1.4025</v>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>排名从3→新第1不等,调出</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-08-06 10:57</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>中概互联网ETF易方达</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>sh513050</t>
+        </is>
+      </c>
+      <c r="E236" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="F236" t="n">
+        <v>1.5142</v>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>动量排名第1/38</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backtest/results_172/七星172_交易记录_2026.xlsx
+++ b/backtest/results_172/七星172_交易记录_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H236"/>
+  <dimension ref="A1:H254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8446,6 +8446,618 @@
       </c>
       <c r="H236" t="inlineStr"/>
     </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-08-10 13:02</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>中概互联网ETF易方达</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>sh513050</t>
+        </is>
+      </c>
+      <c r="E237" t="n">
+        <v>1.172</v>
+      </c>
+      <c r="F237" t="n">
+        <v>0.9389</v>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>排名从1→新第1不等,调出</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-08-10 13:02</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>自由现金流ETF华夏</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>sz159201</t>
+        </is>
+      </c>
+      <c r="E238" t="n">
+        <v>1.181</v>
+      </c>
+      <c r="F238" t="n">
+        <v>0.9422</v>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>动量排名第1/38</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-08-11 10:58</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>自由现金流ETF华夏</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>sz159201</t>
+        </is>
+      </c>
+      <c r="E239" t="n">
+        <v>1.189</v>
+      </c>
+      <c r="F239" t="n">
+        <v>0.9956</v>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>排名从3→新第1不等,调出</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-08-11 10:58</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>白银LOF国投</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>sz161226</t>
+        </is>
+      </c>
+      <c r="E240" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="F240" t="n">
+        <v>1.5112</v>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>动量排名第1/38</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-08-12 10:57</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>白银LOF国投</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>sz161226</t>
+        </is>
+      </c>
+      <c r="E241" t="n">
+        <v>1.911</v>
+      </c>
+      <c r="F241" t="n">
+        <v>0.7698</v>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>被过滤规则拦截调出: 盈利保护</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-08-12 10:57</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>自由现金流ETF华夏</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>sz159201</t>
+        </is>
+      </c>
+      <c r="E242" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="F242" t="n">
+        <v>1.0171</v>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>动量排名第1/38</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-08-13 10:57</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>自由现金流ETF华夏</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>sz159201</t>
+        </is>
+      </c>
+      <c r="E243" t="n">
+        <v>1.177</v>
+      </c>
+      <c r="F243" t="n">
+        <v>0.8243</v>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>排名从3→新第1不等,调出</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-08-13 10:57</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>标普500ETF博时</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>sh513500</t>
+        </is>
+      </c>
+      <c r="E244" t="n">
+        <v>2.725</v>
+      </c>
+      <c r="F244" t="n">
+        <v>0.9115</v>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>动量排名第1/38</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-08-19 10:57</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>标普500ETF博时</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>sh513500</t>
+        </is>
+      </c>
+      <c r="E245" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="F245" t="n">
+        <v>1.2357</v>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>排名从3→新第1不等,调出</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-08-19 10:57</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>黄金ETF华安</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>sh518880</t>
+        </is>
+      </c>
+      <c r="E246" t="n">
+        <v>8.987</v>
+      </c>
+      <c r="F246" t="n">
+        <v>1.4419</v>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>动量排名第1/38</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-08-20 10:58</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>黄金ETF华安</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>sh518880</t>
+        </is>
+      </c>
+      <c r="E247" t="n">
+        <v>9.227</v>
+      </c>
+      <c r="F247" t="n">
+        <v>1.6218</v>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>排名从2→新第1不等,调出</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-08-20 10:58</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>中证2000ETF华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>sh563300</t>
+        </is>
+      </c>
+      <c r="E248" t="n">
+        <v>1.411</v>
+      </c>
+      <c r="F248" t="n">
+        <v>1.8517</v>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>动量排名第1/38</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-08-24 10:58</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>中证2000ETF华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>sh563300</t>
+        </is>
+      </c>
+      <c r="E249" t="n">
+        <v>1.376</v>
+      </c>
+      <c r="F249" t="n">
+        <v>1.5127</v>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>排名从2→新第1不等,调出</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-08-24 10:58</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>纳指生物科技ETF汇添富</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>sh513290</t>
+        </is>
+      </c>
+      <c r="E250" t="n">
+        <v>1.809</v>
+      </c>
+      <c r="F250" t="n">
+        <v>2.857</v>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>动量排名第1/38</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-08-27 10:58</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>纳指生物科技ETF汇添富</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>sh513290</t>
+        </is>
+      </c>
+      <c r="E251" t="n">
+        <v>1.833</v>
+      </c>
+      <c r="F251" t="n">
+        <v>4.618</v>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>被过滤规则拦截调出: 盈利保护</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-08-27 10:58</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>黄金ETF华安</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>sh518880</t>
+        </is>
+      </c>
+      <c r="E252" t="n">
+        <v>9.507999999999999</v>
+      </c>
+      <c r="F252" t="n">
+        <v>3.0038</v>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>动量排名第1/38</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-08-28 10:56</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>黄金ETF华安</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>sh518880</t>
+        </is>
+      </c>
+      <c r="E253" t="n">
+        <v>9.419</v>
+      </c>
+      <c r="F253" t="n">
+        <v>2.901</v>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>排名从2→新第1不等,调出</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026-08-28 10:56</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>纳指生物科技ETF汇添富</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>sh513290</t>
+        </is>
+      </c>
+      <c r="E254" t="n">
+        <v>1.817</v>
+      </c>
+      <c r="F254" t="n">
+        <v>4.5929</v>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>动量排名第1/38</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backtest/results_172/七星172_交易记录_2026.xlsx
+++ b/backtest/results_172/七星172_交易记录_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H254"/>
+  <dimension ref="A1:H256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9058,6 +9058,74 @@
       </c>
       <c r="H254" t="inlineStr"/>
     </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2026-09-03 13:05</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>纳指生物科技ETF汇添富</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>sh513290</t>
+        </is>
+      </c>
+      <c r="E255" t="n">
+        <v>1.836</v>
+      </c>
+      <c r="F255" t="n">
+        <v>2.3255</v>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>排名从3→新第1不等,调出</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026-09-03 13:05</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>豆粕ETF华夏</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>sz159985</t>
+        </is>
+      </c>
+      <c r="E256" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="F256" t="n">
+        <v>2.6601</v>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>动量排名第1/38</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
